--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,6 +707,234 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>667.4299999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>707.79</v>
+      </c>
+      <c r="E8" t="n">
+        <v>667.4299999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>707.79</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H8" t="n">
+        <v>682.39</v>
+      </c>
+      <c r="I8" t="n">
+        <v>80</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>665.1900000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>700.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>665.1900000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>700.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H9" t="n">
+        <v>682.39</v>
+      </c>
+      <c r="I9" t="n">
+        <v>80</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>662.95</v>
+      </c>
+      <c r="D10" t="n">
+        <v>692.23</v>
+      </c>
+      <c r="E10" t="n">
+        <v>662.95</v>
+      </c>
+      <c r="F10" t="n">
+        <v>692.23</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H10" t="n">
+        <v>682.39</v>
+      </c>
+      <c r="I10" t="n">
+        <v>80</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>692.74</v>
+      </c>
+      <c r="D11" t="n">
+        <v>704.12</v>
+      </c>
+      <c r="E11" t="n">
+        <v>681.46</v>
+      </c>
+      <c r="F11" t="n">
+        <v>704.12</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H11" t="n">
+        <v>682.39</v>
+      </c>
+      <c r="I11" t="n">
+        <v>80</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>690.41</v>
+      </c>
+      <c r="D12" t="n">
+        <v>696.77</v>
+      </c>
+      <c r="E12" t="n">
+        <v>681.46</v>
+      </c>
+      <c r="F12" t="n">
+        <v>696.77</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="H12" t="n">
+        <v>682.39</v>
+      </c>
+      <c r="I12" t="n">
+        <v>80</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>688.09</v>
+      </c>
+      <c r="D13" t="n">
+        <v>693.73</v>
+      </c>
+      <c r="E13" t="n">
+        <v>673.51</v>
+      </c>
+      <c r="F13" t="n">
+        <v>688.64</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H13" t="n">
+        <v>682.39</v>
+      </c>
+      <c r="I13" t="n">
+        <v>80</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -721,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,6 +1229,234 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="D8" t="n">
+        <v>295.05</v>
+      </c>
+      <c r="E8" t="n">
+        <v>254.49</v>
+      </c>
+      <c r="F8" t="n">
+        <v>292.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>266.18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>291.24</v>
+      </c>
+      <c r="D9" t="n">
+        <v>291.24</v>
+      </c>
+      <c r="E9" t="n">
+        <v>254.49</v>
+      </c>
+      <c r="F9" t="n">
+        <v>279.36</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="H9" t="n">
+        <v>266.18</v>
+      </c>
+      <c r="I9" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>287.42</v>
+      </c>
+      <c r="D10" t="n">
+        <v>287.42</v>
+      </c>
+      <c r="E10" t="n">
+        <v>244.04</v>
+      </c>
+      <c r="F10" t="n">
+        <v>267.89</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H10" t="n">
+        <v>266.18</v>
+      </c>
+      <c r="I10" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>263.35</v>
+      </c>
+      <c r="D11" t="n">
+        <v>277.86</v>
+      </c>
+      <c r="E11" t="n">
+        <v>252.53</v>
+      </c>
+      <c r="F11" t="n">
+        <v>277.86</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H11" t="n">
+        <v>266.18</v>
+      </c>
+      <c r="I11" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>259.94</v>
+      </c>
+      <c r="D12" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>252.53</v>
+      </c>
+      <c r="F12" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>266.18</v>
+      </c>
+      <c r="I12" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>256.54</v>
+      </c>
+      <c r="D13" t="n">
+        <v>260.89</v>
+      </c>
+      <c r="E13" t="n">
+        <v>242.16</v>
+      </c>
+      <c r="F13" t="n">
+        <v>254.89</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>266.18</v>
+      </c>
+      <c r="I13" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1298,6 +1754,234 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>470.97</v>
+      </c>
+      <c r="D8" t="n">
+        <v>504.65</v>
+      </c>
+      <c r="E8" t="n">
+        <v>406.16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>480.55</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="H8" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I8" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>496.51</v>
+      </c>
+      <c r="E9" t="n">
+        <v>406.16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>472.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="H9" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I9" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>466.53</v>
+      </c>
+      <c r="D10" t="n">
+        <v>496.51</v>
+      </c>
+      <c r="E10" t="n">
+        <v>400.14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>465.78</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I10" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>425.17</v>
+      </c>
+      <c r="D11" t="n">
+        <v>425.17</v>
+      </c>
+      <c r="E11" t="n">
+        <v>392.93</v>
+      </c>
+      <c r="F11" t="n">
+        <v>392.93</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>423.17</v>
+      </c>
+      <c r="D12" t="n">
+        <v>423.17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>386.59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>386.59</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I12" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>421.16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>421.16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>380.86</v>
+      </c>
+      <c r="F13" t="n">
+        <v>380.86</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I13" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,6 +935,234 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>694.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>699.98</v>
+      </c>
+      <c r="E14" t="n">
+        <v>689.96</v>
+      </c>
+      <c r="F14" t="n">
+        <v>693.03</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="H14" t="n">
+        <v>687.35</v>
+      </c>
+      <c r="I14" t="n">
+        <v>80</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>692.52</v>
+      </c>
+      <c r="D15" t="n">
+        <v>692.52</v>
+      </c>
+      <c r="E15" t="n">
+        <v>684.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>684.9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="H15" t="n">
+        <v>687.35</v>
+      </c>
+      <c r="I15" t="n">
+        <v>80</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>690.15</v>
+      </c>
+      <c r="D16" t="n">
+        <v>691.77</v>
+      </c>
+      <c r="E16" t="n">
+        <v>677.54</v>
+      </c>
+      <c r="F16" t="n">
+        <v>677.54</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="H16" t="n">
+        <v>687.35</v>
+      </c>
+      <c r="I16" t="n">
+        <v>80</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>694.9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>699.97</v>
+      </c>
+      <c r="E17" t="n">
+        <v>689.9400000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>693.01</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H17" t="n">
+        <v>687.35</v>
+      </c>
+      <c r="I17" t="n">
+        <v>80</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>692.52</v>
+      </c>
+      <c r="D18" t="n">
+        <v>692.52</v>
+      </c>
+      <c r="E18" t="n">
+        <v>684.87</v>
+      </c>
+      <c r="F18" t="n">
+        <v>684.87</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="H18" t="n">
+        <v>687.35</v>
+      </c>
+      <c r="I18" t="n">
+        <v>80</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>690.15</v>
+      </c>
+      <c r="D19" t="n">
+        <v>691.76</v>
+      </c>
+      <c r="E19" t="n">
+        <v>677.52</v>
+      </c>
+      <c r="F19" t="n">
+        <v>677.52</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="H19" t="n">
+        <v>687.35</v>
+      </c>
+      <c r="I19" t="n">
+        <v>80</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -949,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,6 +1685,234 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>259.65</v>
+      </c>
+      <c r="D14" t="n">
+        <v>288.96</v>
+      </c>
+      <c r="E14" t="n">
+        <v>256.01</v>
+      </c>
+      <c r="F14" t="n">
+        <v>288.96</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="H14" t="n">
+        <v>272.14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>256.72</v>
+      </c>
+      <c r="D15" t="n">
+        <v>276.95</v>
+      </c>
+      <c r="E15" t="n">
+        <v>256.01</v>
+      </c>
+      <c r="F15" t="n">
+        <v>276.95</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>272.14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>253.79</v>
+      </c>
+      <c r="D16" t="n">
+        <v>268.08</v>
+      </c>
+      <c r="E16" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>268.08</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H16" t="n">
+        <v>272.14</v>
+      </c>
+      <c r="I16" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>259.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>288.96</v>
+      </c>
+      <c r="E17" t="n">
+        <v>256.05</v>
+      </c>
+      <c r="F17" t="n">
+        <v>288.96</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="H17" t="n">
+        <v>272.14</v>
+      </c>
+      <c r="I17" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>256.77</v>
+      </c>
+      <c r="D18" t="n">
+        <v>276.95</v>
+      </c>
+      <c r="E18" t="n">
+        <v>256.05</v>
+      </c>
+      <c r="F18" t="n">
+        <v>276.95</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>272.14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>253.83</v>
+      </c>
+      <c r="D19" t="n">
+        <v>268.08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>247.85</v>
+      </c>
+      <c r="F19" t="n">
+        <v>268.08</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H19" t="n">
+        <v>272.14</v>
+      </c>
+      <c r="I19" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,6 +2438,234 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>433.05</v>
+      </c>
+      <c r="D14" t="n">
+        <v>433.05</v>
+      </c>
+      <c r="E14" t="n">
+        <v>400.04</v>
+      </c>
+      <c r="F14" t="n">
+        <v>400.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H14" t="n">
+        <v>389</v>
+      </c>
+      <c r="I14" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>430.64</v>
+      </c>
+      <c r="D15" t="n">
+        <v>430.64</v>
+      </c>
+      <c r="E15" t="n">
+        <v>393.15</v>
+      </c>
+      <c r="F15" t="n">
+        <v>393.15</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="n">
+        <v>389</v>
+      </c>
+      <c r="I15" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>428.23</v>
+      </c>
+      <c r="D16" t="n">
+        <v>428.23</v>
+      </c>
+      <c r="E16" t="n">
+        <v>385.54</v>
+      </c>
+      <c r="F16" t="n">
+        <v>385.54</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="H16" t="n">
+        <v>389</v>
+      </c>
+      <c r="I16" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>433.07</v>
+      </c>
+      <c r="D17" t="n">
+        <v>433.07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>400.17</v>
+      </c>
+      <c r="F17" t="n">
+        <v>400.17</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H17" t="n">
+        <v>389</v>
+      </c>
+      <c r="I17" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>430.66</v>
+      </c>
+      <c r="D18" t="n">
+        <v>430.66</v>
+      </c>
+      <c r="E18" t="n">
+        <v>393.28</v>
+      </c>
+      <c r="F18" t="n">
+        <v>393.28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>389</v>
+      </c>
+      <c r="I18" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>428.26</v>
+      </c>
+      <c r="D19" t="n">
+        <v>428.26</v>
+      </c>
+      <c r="E19" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="F19" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="H19" t="n">
+        <v>389</v>
+      </c>
+      <c r="I19" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1163,6 +1163,120 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:24</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>693.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>696.51</v>
+      </c>
+      <c r="E20" t="n">
+        <v>685.76</v>
+      </c>
+      <c r="F20" t="n">
+        <v>692.96</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H20" t="n">
+        <v>684.54</v>
+      </c>
+      <c r="I20" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:24</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>690.83</v>
+      </c>
+      <c r="D21" t="n">
+        <v>690.83</v>
+      </c>
+      <c r="E21" t="n">
+        <v>683.48</v>
+      </c>
+      <c r="F21" t="n">
+        <v>683.48</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H21" t="n">
+        <v>684.54</v>
+      </c>
+      <c r="I21" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:24</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>688.0700000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>688.0700000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>674.91</v>
+      </c>
+      <c r="F22" t="n">
+        <v>674.91</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="H22" t="n">
+        <v>684.54</v>
+      </c>
+      <c r="I22" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,6 +2027,120 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>266.12</v>
+      </c>
+      <c r="D20" t="n">
+        <v>277.25</v>
+      </c>
+      <c r="E20" t="n">
+        <v>260.01</v>
+      </c>
+      <c r="F20" t="n">
+        <v>273.19</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H20" t="n">
+        <v>268.09</v>
+      </c>
+      <c r="I20" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>264.27</v>
+      </c>
+      <c r="D21" t="n">
+        <v>270.08</v>
+      </c>
+      <c r="E21" t="n">
+        <v>260.01</v>
+      </c>
+      <c r="F21" t="n">
+        <v>266.13</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="H21" t="n">
+        <v>268.09</v>
+      </c>
+      <c r="I21" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>262.42</v>
+      </c>
+      <c r="D22" t="n">
+        <v>270.08</v>
+      </c>
+      <c r="E22" t="n">
+        <v>254.91</v>
+      </c>
+      <c r="F22" t="n">
+        <v>260.91</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="H22" t="n">
+        <v>268.09</v>
+      </c>
+      <c r="I22" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1927,7 +2155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2666,6 +2894,120 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>419.86</v>
+      </c>
+      <c r="D20" t="n">
+        <v>421.96</v>
+      </c>
+      <c r="E20" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H20" t="n">
+        <v>395.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>415.64</v>
+      </c>
+      <c r="D21" t="n">
+        <v>415.64</v>
+      </c>
+      <c r="E21" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>395.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>411.41</v>
+      </c>
+      <c r="D22" t="n">
+        <v>411.41</v>
+      </c>
+      <c r="E22" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="F22" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-6.21</v>
+      </c>
+      <c r="H22" t="n">
+        <v>395.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,6 +481,36 @@
           <t>Signal</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Error %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Dir Accuracy %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>In Range %</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Matched Preds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1277,6 +1307,348 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>678.16</v>
+      </c>
+      <c r="D23" t="n">
+        <v>694.96</v>
+      </c>
+      <c r="E23" t="n">
+        <v>668.79</v>
+      </c>
+      <c r="F23" t="n">
+        <v>691.83</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="H23" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I23" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>674.5700000000001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>683.54</v>
+      </c>
+      <c r="E24" t="n">
+        <v>668.79</v>
+      </c>
+      <c r="F24" t="n">
+        <v>680.45</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="H24" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I24" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>670.97</v>
+      </c>
+      <c r="D25" t="n">
+        <v>683.54</v>
+      </c>
+      <c r="E25" t="n">
+        <v>656.4299999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>667.88</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H25" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I25" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>665.04</v>
+      </c>
+      <c r="D26" t="n">
+        <v>706.11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>665.04</v>
+      </c>
+      <c r="F26" t="n">
+        <v>681.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="H26" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I26" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>661.51</v>
+      </c>
+      <c r="D27" t="n">
+        <v>694.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>661.51</v>
+      </c>
+      <c r="F27" t="n">
+        <v>670.39</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="H27" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I27" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>657.98</v>
+      </c>
+      <c r="D28" t="n">
+        <v>694.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>657.98</v>
+      </c>
+      <c r="F28" t="n">
+        <v>658</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I28" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>687.9400000000001</v>
+      </c>
+      <c r="D29" t="n">
+        <v>694.4299999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>662.15</v>
+      </c>
+      <c r="F29" t="n">
+        <v>662.15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H29" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I29" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>684.29</v>
+      </c>
+      <c r="D30" t="n">
+        <v>690.02</v>
+      </c>
+      <c r="E30" t="n">
+        <v>651.26</v>
+      </c>
+      <c r="F30" t="n">
+        <v>651.26</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H30" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I30" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>680.64</v>
+      </c>
+      <c r="D31" t="n">
+        <v>683.01</v>
+      </c>
+      <c r="E31" t="n">
+        <v>639.22</v>
+      </c>
+      <c r="F31" t="n">
+        <v>639.22</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="H31" t="n">
+        <v>645.09</v>
+      </c>
+      <c r="I31" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1345,6 +1717,36 @@
           <t>Signal</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Error %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Dir Accuracy %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>In Range %</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Matched Preds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2141,6 +2543,348 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>273.85</v>
+      </c>
+      <c r="D23" t="n">
+        <v>275.33</v>
+      </c>
+      <c r="E23" t="n">
+        <v>264.21</v>
+      </c>
+      <c r="F23" t="n">
+        <v>275.33</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I23" t="n">
+        <v>80</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>272.55</v>
+      </c>
+      <c r="D24" t="n">
+        <v>272.55</v>
+      </c>
+      <c r="E24" t="n">
+        <v>264.21</v>
+      </c>
+      <c r="F24" t="n">
+        <v>270.87</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I24" t="n">
+        <v>80</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>271.26</v>
+      </c>
+      <c r="D25" t="n">
+        <v>271.26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>260.28</v>
+      </c>
+      <c r="F25" t="n">
+        <v>266.83</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="H25" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I25" t="n">
+        <v>80</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>257.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>273.75</v>
+      </c>
+      <c r="E26" t="n">
+        <v>256</v>
+      </c>
+      <c r="F26" t="n">
+        <v>263.77</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I26" t="n">
+        <v>80</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>255.88</v>
+      </c>
+      <c r="D27" t="n">
+        <v>269.32</v>
+      </c>
+      <c r="E27" t="n">
+        <v>255.88</v>
+      </c>
+      <c r="F27" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H27" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I27" t="n">
+        <v>80</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>254.66</v>
+      </c>
+      <c r="D28" t="n">
+        <v>269.32</v>
+      </c>
+      <c r="E28" t="n">
+        <v>252.18</v>
+      </c>
+      <c r="F28" t="n">
+        <v>255.63</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H28" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I28" t="n">
+        <v>80</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>266.08</v>
+      </c>
+      <c r="D29" t="n">
+        <v>266.08</v>
+      </c>
+      <c r="E29" t="n">
+        <v>261.18</v>
+      </c>
+      <c r="F29" t="n">
+        <v>261.73</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I29" t="n">
+        <v>80</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>264.82</v>
+      </c>
+      <c r="D30" t="n">
+        <v>264.82</v>
+      </c>
+      <c r="E30" t="n">
+        <v>257.49</v>
+      </c>
+      <c r="F30" t="n">
+        <v>257.49</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H30" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I30" t="n">
+        <v>80</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>263.56</v>
+      </c>
+      <c r="D31" t="n">
+        <v>263.56</v>
+      </c>
+      <c r="E31" t="n">
+        <v>253.65</v>
+      </c>
+      <c r="F31" t="n">
+        <v>253.65</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>252.89</v>
+      </c>
+      <c r="I31" t="n">
+        <v>80</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2209,6 +2953,36 @@
           <t>Signal</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Error %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Dir Accuracy %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>In Range %</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Matched Preds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2247,6 +3021,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2285,6 +3065,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2323,6 +3109,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2361,6 +3153,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2399,6 +3197,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2437,6 +3241,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2475,6 +3285,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2513,6 +3329,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2551,6 +3373,12 @@
           <t>STRONG BUY</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2589,6 +3417,12 @@
           <t>BUY</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2627,6 +3461,12 @@
           <t>BUY</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2665,6 +3505,12 @@
           <t>BUY</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2703,6 +3549,12 @@
           <t>HOLD</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2741,6 +3593,12 @@
           <t>HOLD</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2779,6 +3637,12 @@
           <t>HOLD</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2817,6 +3681,12 @@
           <t>HOLD</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2855,6 +3725,12 @@
           <t>HOLD</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2893,6 +3769,12 @@
           <t>HOLD</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2931,6 +3813,12 @@
           <t>SELL</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2969,6 +3857,12 @@
           <t>SELL</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3007,6 +3901,408 @@
           <t>SELL</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>388.46</v>
+      </c>
+      <c r="D23" t="n">
+        <v>455.39</v>
+      </c>
+      <c r="E23" t="n">
+        <v>388.46</v>
+      </c>
+      <c r="F23" t="n">
+        <v>455.39</v>
+      </c>
+      <c r="G23" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="H23" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I23" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>386.23</v>
+      </c>
+      <c r="D24" t="n">
+        <v>446.48</v>
+      </c>
+      <c r="E24" t="n">
+        <v>386.23</v>
+      </c>
+      <c r="F24" t="n">
+        <v>446.48</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I24" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="D25" t="n">
+        <v>438.41</v>
+      </c>
+      <c r="E25" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="F25" t="n">
+        <v>438.41</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="H25" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I25" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="D26" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="E26" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="F26" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="H26" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I26" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="D27" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="E27" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="F27" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H27" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I27" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="D28" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="E28" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="F28" t="n">
+        <v>368.66</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H28" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I28" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>401.16</v>
+      </c>
+      <c r="D29" t="n">
+        <v>414.18</v>
+      </c>
+      <c r="E29" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I29" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>398.86</v>
+      </c>
+      <c r="D30" t="n">
+        <v>410.69</v>
+      </c>
+      <c r="E30" t="n">
+        <v>388.94</v>
+      </c>
+      <c r="F30" t="n">
+        <v>388.94</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="H30" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I30" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>396.56</v>
+      </c>
+      <c r="D31" t="n">
+        <v>406.08</v>
+      </c>
+      <c r="E31" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="F31" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H31" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I31" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPY" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAPL" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MSFT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AMZN" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1649,6 +1650,462 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>673.29</v>
+      </c>
+      <c r="D32" t="n">
+        <v>684.45</v>
+      </c>
+      <c r="E32" t="n">
+        <v>673.29</v>
+      </c>
+      <c r="F32" t="n">
+        <v>679.41</v>
+      </c>
+      <c r="G32" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="H32" t="n">
+        <v>639.3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>669.6799999999999</v>
+      </c>
+      <c r="D33" t="n">
+        <v>674.76</v>
+      </c>
+      <c r="E33" t="n">
+        <v>666.92</v>
+      </c>
+      <c r="F33" t="n">
+        <v>666.92</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H33" t="n">
+        <v>639.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>666.0599999999999</v>
+      </c>
+      <c r="D34" t="n">
+        <v>671.87</v>
+      </c>
+      <c r="E34" t="n">
+        <v>655.63</v>
+      </c>
+      <c r="F34" t="n">
+        <v>655.63</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H34" t="n">
+        <v>639.3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>673.0599999999999</v>
+      </c>
+      <c r="D35" t="n">
+        <v>684.25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>673.0599999999999</v>
+      </c>
+      <c r="F35" t="n">
+        <v>679.35</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="H35" t="n">
+        <v>639.14</v>
+      </c>
+      <c r="I35" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>669.4400000000001</v>
+      </c>
+      <c r="D36" t="n">
+        <v>674.8200000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>666.86</v>
+      </c>
+      <c r="F36" t="n">
+        <v>666.86</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="H36" t="n">
+        <v>639.14</v>
+      </c>
+      <c r="I36" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>665.8200000000001</v>
+      </c>
+      <c r="D37" t="n">
+        <v>671.67</v>
+      </c>
+      <c r="E37" t="n">
+        <v>655.5599999999999</v>
+      </c>
+      <c r="F37" t="n">
+        <v>655.5599999999999</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H37" t="n">
+        <v>639.14</v>
+      </c>
+      <c r="I37" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>674.03</v>
+      </c>
+      <c r="D38" t="n">
+        <v>683.98</v>
+      </c>
+      <c r="E38" t="n">
+        <v>674.03</v>
+      </c>
+      <c r="F38" t="n">
+        <v>680.08</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="H38" t="n">
+        <v>639.47</v>
+      </c>
+      <c r="I38" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>670.41</v>
+      </c>
+      <c r="D39" t="n">
+        <v>674.83</v>
+      </c>
+      <c r="E39" t="n">
+        <v>667.6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>667.6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H39" t="n">
+        <v>639.47</v>
+      </c>
+      <c r="I39" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>666.8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>671.42</v>
+      </c>
+      <c r="E40" t="n">
+        <v>656.3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>656.3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H40" t="n">
+        <v>639.47</v>
+      </c>
+      <c r="I40" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>674.72</v>
+      </c>
+      <c r="D41" t="n">
+        <v>683.61</v>
+      </c>
+      <c r="E41" t="n">
+        <v>674.41</v>
+      </c>
+      <c r="F41" t="n">
+        <v>680.23</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="H41" t="n">
+        <v>638.92</v>
+      </c>
+      <c r="I41" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>671.08</v>
+      </c>
+      <c r="D42" t="n">
+        <v>674.41</v>
+      </c>
+      <c r="E42" t="n">
+        <v>667.71</v>
+      </c>
+      <c r="F42" t="n">
+        <v>667.71</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H42" t="n">
+        <v>638.92</v>
+      </c>
+      <c r="I42" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>667.45</v>
+      </c>
+      <c r="D43" t="n">
+        <v>671.03</v>
+      </c>
+      <c r="E43" t="n">
+        <v>656.39</v>
+      </c>
+      <c r="F43" t="n">
+        <v>656.39</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="H43" t="n">
+        <v>638.92</v>
+      </c>
+      <c r="I43" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
@@ -1663,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2885,6 +3342,462 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>267.94</v>
+      </c>
+      <c r="D32" t="n">
+        <v>267.94</v>
+      </c>
+      <c r="E32" t="n">
+        <v>250.11</v>
+      </c>
+      <c r="F32" t="n">
+        <v>263</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="H32" t="n">
+        <v>252.29</v>
+      </c>
+      <c r="I32" t="n">
+        <v>80</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>266.79</v>
+      </c>
+      <c r="D33" t="n">
+        <v>266.79</v>
+      </c>
+      <c r="E33" t="n">
+        <v>250.11</v>
+      </c>
+      <c r="F33" t="n">
+        <v>259.11</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>252.29</v>
+      </c>
+      <c r="I33" t="n">
+        <v>80</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>265.63</v>
+      </c>
+      <c r="D34" t="n">
+        <v>265.63</v>
+      </c>
+      <c r="E34" t="n">
+        <v>246.72</v>
+      </c>
+      <c r="F34" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H34" t="n">
+        <v>252.29</v>
+      </c>
+      <c r="I34" t="n">
+        <v>80</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>268.18</v>
+      </c>
+      <c r="D35" t="n">
+        <v>268.18</v>
+      </c>
+      <c r="E35" t="n">
+        <v>249.74</v>
+      </c>
+      <c r="F35" t="n">
+        <v>262.75</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="H35" t="n">
+        <v>252.26</v>
+      </c>
+      <c r="I35" t="n">
+        <v>80</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>267.03</v>
+      </c>
+      <c r="D36" t="n">
+        <v>267.03</v>
+      </c>
+      <c r="E36" t="n">
+        <v>249.74</v>
+      </c>
+      <c r="F36" t="n">
+        <v>258.87</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H36" t="n">
+        <v>252.26</v>
+      </c>
+      <c r="I36" t="n">
+        <v>80</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>265.87</v>
+      </c>
+      <c r="D37" t="n">
+        <v>265.87</v>
+      </c>
+      <c r="E37" t="n">
+        <v>246.35</v>
+      </c>
+      <c r="F37" t="n">
+        <v>255.35</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="H37" t="n">
+        <v>252.26</v>
+      </c>
+      <c r="I37" t="n">
+        <v>80</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>267.84</v>
+      </c>
+      <c r="D38" t="n">
+        <v>267.84</v>
+      </c>
+      <c r="E38" t="n">
+        <v>250.44</v>
+      </c>
+      <c r="F38" t="n">
+        <v>263.24</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H38" t="n">
+        <v>252.31</v>
+      </c>
+      <c r="I38" t="n">
+        <v>80</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>266.68</v>
+      </c>
+      <c r="D39" t="n">
+        <v>266.68</v>
+      </c>
+      <c r="E39" t="n">
+        <v>250.44</v>
+      </c>
+      <c r="F39" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H39" t="n">
+        <v>252.31</v>
+      </c>
+      <c r="I39" t="n">
+        <v>80</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>265.53</v>
+      </c>
+      <c r="D40" t="n">
+        <v>265.53</v>
+      </c>
+      <c r="E40" t="n">
+        <v>247.04</v>
+      </c>
+      <c r="F40" t="n">
+        <v>255.83</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H40" t="n">
+        <v>252.31</v>
+      </c>
+      <c r="I40" t="n">
+        <v>80</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>267.86</v>
+      </c>
+      <c r="D41" t="n">
+        <v>267.86</v>
+      </c>
+      <c r="E41" t="n">
+        <v>250.53</v>
+      </c>
+      <c r="F41" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H41" t="n">
+        <v>251.93</v>
+      </c>
+      <c r="I41" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>266.7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>250.53</v>
+      </c>
+      <c r="F42" t="n">
+        <v>259.38</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H42" t="n">
+        <v>251.93</v>
+      </c>
+      <c r="I42" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>265.54</v>
+      </c>
+      <c r="D43" t="n">
+        <v>265.54</v>
+      </c>
+      <c r="E43" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>255.83</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H43" t="n">
+        <v>251.93</v>
+      </c>
+      <c r="I43" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2899,7 +3812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3019,6 +3932,1698 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:23:54</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>431.34</v>
+      </c>
+      <c r="D3" t="n">
+        <v>431.34</v>
+      </c>
+      <c r="E3" t="n">
+        <v>403.03</v>
+      </c>
+      <c r="F3" t="n">
+        <v>410.08</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="H3" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I3" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:23:54</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>429.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>429.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>397.05</v>
+      </c>
+      <c r="F4" t="n">
+        <v>403.99</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="H4" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I4" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:30:23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>428.83</v>
+      </c>
+      <c r="D5" t="n">
+        <v>445.44</v>
+      </c>
+      <c r="E5" t="n">
+        <v>418.01</v>
+      </c>
+      <c r="F5" t="n">
+        <v>445.44</v>
+      </c>
+      <c r="G5" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="H5" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I5" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:30:23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>426.81</v>
+      </c>
+      <c r="D6" t="n">
+        <v>438.26</v>
+      </c>
+      <c r="E6" t="n">
+        <v>418.01</v>
+      </c>
+      <c r="F6" t="n">
+        <v>438.26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="H6" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I6" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:30:23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>424.79</v>
+      </c>
+      <c r="D7" t="n">
+        <v>431.75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>411.81</v>
+      </c>
+      <c r="F7" t="n">
+        <v>431.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I7" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>470.97</v>
+      </c>
+      <c r="D8" t="n">
+        <v>504.65</v>
+      </c>
+      <c r="E8" t="n">
+        <v>406.16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>480.55</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="H8" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I8" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>496.51</v>
+      </c>
+      <c r="E9" t="n">
+        <v>406.16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>472.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="H9" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I9" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-24 18:57:21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>466.53</v>
+      </c>
+      <c r="D10" t="n">
+        <v>496.51</v>
+      </c>
+      <c r="E10" t="n">
+        <v>400.14</v>
+      </c>
+      <c r="F10" t="n">
+        <v>465.78</v>
+      </c>
+      <c r="G10" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I10" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>425.17</v>
+      </c>
+      <c r="D11" t="n">
+        <v>425.17</v>
+      </c>
+      <c r="E11" t="n">
+        <v>392.93</v>
+      </c>
+      <c r="F11" t="n">
+        <v>392.93</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>423.17</v>
+      </c>
+      <c r="D12" t="n">
+        <v>423.17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>386.59</v>
+      </c>
+      <c r="F12" t="n">
+        <v>386.59</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I12" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-24 19:41:14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>421.16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>421.16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>380.86</v>
+      </c>
+      <c r="F13" t="n">
+        <v>380.86</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="I13" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>433.05</v>
+      </c>
+      <c r="D14" t="n">
+        <v>433.05</v>
+      </c>
+      <c r="E14" t="n">
+        <v>400.04</v>
+      </c>
+      <c r="F14" t="n">
+        <v>400.04</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H14" t="n">
+        <v>389</v>
+      </c>
+      <c r="I14" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>430.64</v>
+      </c>
+      <c r="D15" t="n">
+        <v>430.64</v>
+      </c>
+      <c r="E15" t="n">
+        <v>393.15</v>
+      </c>
+      <c r="F15" t="n">
+        <v>393.15</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H15" t="n">
+        <v>389</v>
+      </c>
+      <c r="I15" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:56:23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>428.23</v>
+      </c>
+      <c r="D16" t="n">
+        <v>428.23</v>
+      </c>
+      <c r="E16" t="n">
+        <v>385.54</v>
+      </c>
+      <c r="F16" t="n">
+        <v>385.54</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="H16" t="n">
+        <v>389</v>
+      </c>
+      <c r="I16" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>433.07</v>
+      </c>
+      <c r="D17" t="n">
+        <v>433.07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>400.17</v>
+      </c>
+      <c r="F17" t="n">
+        <v>400.17</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H17" t="n">
+        <v>389</v>
+      </c>
+      <c r="I17" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>430.66</v>
+      </c>
+      <c r="D18" t="n">
+        <v>430.66</v>
+      </c>
+      <c r="E18" t="n">
+        <v>393.28</v>
+      </c>
+      <c r="F18" t="n">
+        <v>393.28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>389</v>
+      </c>
+      <c r="I18" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-25 13:57:30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>428.26</v>
+      </c>
+      <c r="D19" t="n">
+        <v>428.26</v>
+      </c>
+      <c r="E19" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="F19" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="H19" t="n">
+        <v>389</v>
+      </c>
+      <c r="I19" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>419.86</v>
+      </c>
+      <c r="D20" t="n">
+        <v>421.96</v>
+      </c>
+      <c r="E20" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>396.18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H20" t="n">
+        <v>395.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>415.64</v>
+      </c>
+      <c r="D21" t="n">
+        <v>415.64</v>
+      </c>
+      <c r="E21" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>382.7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>395.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-28 01:38:25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>411.41</v>
+      </c>
+      <c r="D22" t="n">
+        <v>411.41</v>
+      </c>
+      <c r="E22" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="F22" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-6.21</v>
+      </c>
+      <c r="H22" t="n">
+        <v>395.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>388.46</v>
+      </c>
+      <c r="D23" t="n">
+        <v>455.39</v>
+      </c>
+      <c r="E23" t="n">
+        <v>388.46</v>
+      </c>
+      <c r="F23" t="n">
+        <v>455.39</v>
+      </c>
+      <c r="G23" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="H23" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I23" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>386.23</v>
+      </c>
+      <c r="D24" t="n">
+        <v>446.48</v>
+      </c>
+      <c r="E24" t="n">
+        <v>386.23</v>
+      </c>
+      <c r="F24" t="n">
+        <v>446.48</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I24" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:41:46</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="D25" t="n">
+        <v>438.41</v>
+      </c>
+      <c r="E25" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="F25" t="n">
+        <v>438.41</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="H25" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I25" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="D26" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="E26" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="F26" t="n">
+        <v>382.93</v>
+      </c>
+      <c r="G26" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="H26" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I26" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="D27" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="E27" t="n">
+        <v>363.44</v>
+      </c>
+      <c r="F27" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="H27" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I27" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:46:20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="D28" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="E28" t="n">
+        <v>361.35</v>
+      </c>
+      <c r="F28" t="n">
+        <v>368.66</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H28" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I28" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>401.16</v>
+      </c>
+      <c r="D29" t="n">
+        <v>414.18</v>
+      </c>
+      <c r="E29" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="F29" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I29" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>398.86</v>
+      </c>
+      <c r="D30" t="n">
+        <v>410.69</v>
+      </c>
+      <c r="E30" t="n">
+        <v>388.94</v>
+      </c>
+      <c r="F30" t="n">
+        <v>388.94</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="H30" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I30" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-27 23:50:22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>396.56</v>
+      </c>
+      <c r="D31" t="n">
+        <v>406.08</v>
+      </c>
+      <c r="E31" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="F31" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H31" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="I31" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="D32" t="n">
+        <v>415.83</v>
+      </c>
+      <c r="E32" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="F32" t="n">
+        <v>400.66</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="H32" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="I32" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="D33" t="n">
+        <v>415.83</v>
+      </c>
+      <c r="E33" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="F33" t="n">
+        <v>392.99</v>
+      </c>
+      <c r="G33" t="n">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="I33" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:18:33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="D34" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="F34" t="n">
+        <v>386.06</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="H34" t="n">
+        <v>360.43</v>
+      </c>
+      <c r="I34" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:07</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>389.62</v>
+      </c>
+      <c r="D35" t="n">
+        <v>415.55</v>
+      </c>
+      <c r="E35" t="n">
+        <v>389.62</v>
+      </c>
+      <c r="F35" t="n">
+        <v>400.29</v>
+      </c>
+      <c r="G35" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="H35" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="I35" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:07</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>387.44</v>
+      </c>
+      <c r="D36" t="n">
+        <v>415.55</v>
+      </c>
+      <c r="E36" t="n">
+        <v>387.44</v>
+      </c>
+      <c r="F36" t="n">
+        <v>392.64</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="H36" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="I36" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:07</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>385.26</v>
+      </c>
+      <c r="D37" t="n">
+        <v>408.21</v>
+      </c>
+      <c r="E37" t="n">
+        <v>385.26</v>
+      </c>
+      <c r="F37" t="n">
+        <v>385.71</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="H37" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="I37" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>391.52</v>
+      </c>
+      <c r="D38" t="n">
+        <v>416.88</v>
+      </c>
+      <c r="E38" t="n">
+        <v>391.52</v>
+      </c>
+      <c r="F38" t="n">
+        <v>401.33</v>
+      </c>
+      <c r="G38" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="H38" t="n">
+        <v>360.15</v>
+      </c>
+      <c r="I38" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="D39" t="n">
+        <v>416.88</v>
+      </c>
+      <c r="E39" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="F39" t="n">
+        <v>393.65</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>360.15</v>
+      </c>
+      <c r="I39" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:23:47</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>387.14</v>
+      </c>
+      <c r="D40" t="n">
+        <v>409.52</v>
+      </c>
+      <c r="E40" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="F40" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="G40" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="H40" t="n">
+        <v>360.15</v>
+      </c>
+      <c r="I40" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>391.47</v>
+      </c>
+      <c r="D41" t="n">
+        <v>416.58</v>
+      </c>
+      <c r="E41" t="n">
+        <v>391.47</v>
+      </c>
+      <c r="F41" t="n">
+        <v>401.15</v>
+      </c>
+      <c r="G41" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="H41" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="I41" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>389.28</v>
+      </c>
+      <c r="D42" t="n">
+        <v>416.58</v>
+      </c>
+      <c r="E42" t="n">
+        <v>389.28</v>
+      </c>
+      <c r="F42" t="n">
+        <v>393.46</v>
+      </c>
+      <c r="G42" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="H42" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="I42" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:28:27</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>387.08</v>
+      </c>
+      <c r="D43" t="n">
+        <v>409.22</v>
+      </c>
+      <c r="E43" t="n">
+        <v>386.5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>386.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>359.88</v>
+      </c>
+      <c r="I43" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Exported At</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Profit %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Error %</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Dir Accuracy %</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>In Range %</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Matched Preds</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-28 00:20:07</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>200.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>237.66</v>
+      </c>
+      <c r="E2" t="n">
+        <v>200.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>223.48</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="H2" t="n">
+        <v>200.59</v>
+      </c>
+      <c r="I2" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -3031,7 +5636,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-24 11:23:54</t>
+          <t>2026-03-28 00:20:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3040,29 +5645,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>431.34</v>
+        <v>198.51</v>
       </c>
       <c r="D3" t="n">
-        <v>431.34</v>
+        <v>230.07</v>
       </c>
       <c r="E3" t="n">
-        <v>403.03</v>
+        <v>198.51</v>
       </c>
       <c r="F3" t="n">
-        <v>410.08</v>
+        <v>216.34</v>
       </c>
       <c r="G3" t="n">
-        <v>6.66</v>
+        <v>7.85</v>
       </c>
       <c r="H3" t="n">
-        <v>384.47</v>
+        <v>200.59</v>
       </c>
       <c r="I3" t="n">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -3075,7 +5680,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-24 11:23:54</t>
+          <t>2026-03-28 00:20:07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3084,29 +5689,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>429.3</v>
+        <v>196.42</v>
       </c>
       <c r="D4" t="n">
-        <v>429.3</v>
+        <v>230.07</v>
       </c>
       <c r="E4" t="n">
-        <v>397.05</v>
+        <v>196.42</v>
       </c>
       <c r="F4" t="n">
-        <v>403.99</v>
+        <v>208.45</v>
       </c>
       <c r="G4" t="n">
-        <v>5.08</v>
+        <v>3.92</v>
       </c>
       <c r="H4" t="n">
-        <v>384.47</v>
+        <v>200.59</v>
       </c>
       <c r="I4" t="n">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -3119,7 +5724,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-24 11:30:23</t>
+          <t>2026-03-28 00:23:47</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3128,29 +5733,29 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>428.83</v>
+        <v>199.04</v>
       </c>
       <c r="D5" t="n">
-        <v>445.44</v>
+        <v>246.65</v>
       </c>
       <c r="E5" t="n">
-        <v>418.01</v>
+        <v>199.04</v>
       </c>
       <c r="F5" t="n">
-        <v>445.44</v>
+        <v>236.27</v>
       </c>
       <c r="G5" t="n">
-        <v>15.86</v>
+        <v>17.64</v>
       </c>
       <c r="H5" t="n">
-        <v>384.47</v>
+        <v>200.84</v>
       </c>
       <c r="I5" t="n">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -3163,7 +5768,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-24 11:30:23</t>
+          <t>2026-03-28 00:23:47</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3172,29 +5777,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>426.81</v>
+        <v>196.97</v>
       </c>
       <c r="D6" t="n">
-        <v>438.26</v>
+        <v>238.8</v>
       </c>
       <c r="E6" t="n">
-        <v>418.01</v>
+        <v>196.97</v>
       </c>
       <c r="F6" t="n">
-        <v>438.26</v>
+        <v>228.75</v>
       </c>
       <c r="G6" t="n">
-        <v>13.99</v>
+        <v>13.89</v>
       </c>
       <c r="H6" t="n">
-        <v>384.47</v>
+        <v>200.84</v>
       </c>
       <c r="I6" t="n">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -3207,7 +5812,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-24 11:30:23</t>
+          <t>2026-03-28 00:23:47</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3216,29 +5821,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>424.79</v>
+        <v>194.9</v>
       </c>
       <c r="D7" t="n">
-        <v>431.75</v>
+        <v>238.8</v>
       </c>
       <c r="E7" t="n">
-        <v>411.81</v>
+        <v>194.9</v>
       </c>
       <c r="F7" t="n">
-        <v>431.75</v>
+        <v>220.43</v>
       </c>
       <c r="G7" t="n">
-        <v>12.3</v>
+        <v>9.75</v>
       </c>
       <c r="H7" t="n">
-        <v>384.47</v>
+        <v>200.84</v>
       </c>
       <c r="I7" t="n">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -3251,7 +5856,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-24 18:57:21</t>
+          <t>2026-03-28 00:28:27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3260,29 +5865,29 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>470.97</v>
+        <v>201.1</v>
       </c>
       <c r="D8" t="n">
-        <v>504.65</v>
+        <v>237.66</v>
       </c>
       <c r="E8" t="n">
-        <v>406.16</v>
+        <v>201.1</v>
       </c>
       <c r="F8" t="n">
-        <v>480.55</v>
+        <v>222.93</v>
       </c>
       <c r="G8" t="n">
-        <v>24.99</v>
+        <v>11.09</v>
       </c>
       <c r="H8" t="n">
-        <v>384.47</v>
+        <v>200.67</v>
       </c>
       <c r="I8" t="n">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -3295,7 +5900,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-24 18:57:21</t>
+          <t>2026-03-28 00:28:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3304,29 +5909,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>468.75</v>
+        <v>199.01</v>
       </c>
       <c r="D9" t="n">
-        <v>496.51</v>
+        <v>230.08</v>
       </c>
       <c r="E9" t="n">
-        <v>406.16</v>
+        <v>199.01</v>
       </c>
       <c r="F9" t="n">
-        <v>472.8</v>
+        <v>215.82</v>
       </c>
       <c r="G9" t="n">
-        <v>22.97</v>
+        <v>7.55</v>
       </c>
       <c r="H9" t="n">
-        <v>384.47</v>
+        <v>200.67</v>
       </c>
       <c r="I9" t="n">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -3339,7 +5944,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-24 18:57:21</t>
+          <t>2026-03-28 00:28:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3348,29 +5953,29 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>466.53</v>
+        <v>196.92</v>
       </c>
       <c r="D10" t="n">
-        <v>496.51</v>
+        <v>230.08</v>
       </c>
       <c r="E10" t="n">
-        <v>400.14</v>
+        <v>196.92</v>
       </c>
       <c r="F10" t="n">
-        <v>465.78</v>
+        <v>207.96</v>
       </c>
       <c r="G10" t="n">
-        <v>21.15</v>
+        <v>3.63</v>
       </c>
       <c r="H10" t="n">
-        <v>384.47</v>
+        <v>200.67</v>
       </c>
       <c r="I10" t="n">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -3380,930 +5985,6 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02-24 19:41:14</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>425.17</v>
-      </c>
-      <c r="D11" t="n">
-        <v>425.17</v>
-      </c>
-      <c r="E11" t="n">
-        <v>392.93</v>
-      </c>
-      <c r="F11" t="n">
-        <v>392.93</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>384.47</v>
-      </c>
-      <c r="I11" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-02-24 19:41:14</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>423.17</v>
-      </c>
-      <c r="D12" t="n">
-        <v>423.17</v>
-      </c>
-      <c r="E12" t="n">
-        <v>386.59</v>
-      </c>
-      <c r="F12" t="n">
-        <v>386.59</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H12" t="n">
-        <v>384.47</v>
-      </c>
-      <c r="I12" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-02-24 19:41:14</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>421.16</v>
-      </c>
-      <c r="D13" t="n">
-        <v>421.16</v>
-      </c>
-      <c r="E13" t="n">
-        <v>380.86</v>
-      </c>
-      <c r="F13" t="n">
-        <v>380.86</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>384.47</v>
-      </c>
-      <c r="I13" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-02-25 13:56:23</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>433.05</v>
-      </c>
-      <c r="D14" t="n">
-        <v>433.05</v>
-      </c>
-      <c r="E14" t="n">
-        <v>400.04</v>
-      </c>
-      <c r="F14" t="n">
-        <v>400.04</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H14" t="n">
-        <v>389</v>
-      </c>
-      <c r="I14" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-02-25 13:56:23</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>430.64</v>
-      </c>
-      <c r="D15" t="n">
-        <v>430.64</v>
-      </c>
-      <c r="E15" t="n">
-        <v>393.15</v>
-      </c>
-      <c r="F15" t="n">
-        <v>393.15</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H15" t="n">
-        <v>389</v>
-      </c>
-      <c r="I15" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-02-25 13:56:23</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>428.23</v>
-      </c>
-      <c r="D16" t="n">
-        <v>428.23</v>
-      </c>
-      <c r="E16" t="n">
-        <v>385.54</v>
-      </c>
-      <c r="F16" t="n">
-        <v>385.54</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="H16" t="n">
-        <v>389</v>
-      </c>
-      <c r="I16" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-02-25 13:57:30</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>433.07</v>
-      </c>
-      <c r="D17" t="n">
-        <v>433.07</v>
-      </c>
-      <c r="E17" t="n">
-        <v>400.17</v>
-      </c>
-      <c r="F17" t="n">
-        <v>400.17</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="H17" t="n">
-        <v>389</v>
-      </c>
-      <c r="I17" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-02-25 13:57:30</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>430.66</v>
-      </c>
-      <c r="D18" t="n">
-        <v>430.66</v>
-      </c>
-      <c r="E18" t="n">
-        <v>393.28</v>
-      </c>
-      <c r="F18" t="n">
-        <v>393.28</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>389</v>
-      </c>
-      <c r="I18" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-02-25 13:57:30</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>428.26</v>
-      </c>
-      <c r="D19" t="n">
-        <v>428.26</v>
-      </c>
-      <c r="E19" t="n">
-        <v>385.67</v>
-      </c>
-      <c r="F19" t="n">
-        <v>385.67</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="H19" t="n">
-        <v>389</v>
-      </c>
-      <c r="I19" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-02-28 01:38:25</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>419.86</v>
-      </c>
-      <c r="D20" t="n">
-        <v>421.96</v>
-      </c>
-      <c r="E20" t="n">
-        <v>396.18</v>
-      </c>
-      <c r="F20" t="n">
-        <v>396.18</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H20" t="n">
-        <v>395.04</v>
-      </c>
-      <c r="I20" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-02-28 01:38:25</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>415.64</v>
-      </c>
-      <c r="D21" t="n">
-        <v>415.64</v>
-      </c>
-      <c r="E21" t="n">
-        <v>382.7</v>
-      </c>
-      <c r="F21" t="n">
-        <v>382.7</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="H21" t="n">
-        <v>395.04</v>
-      </c>
-      <c r="I21" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-02-28 01:38:25</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>411.41</v>
-      </c>
-      <c r="D22" t="n">
-        <v>411.41</v>
-      </c>
-      <c r="E22" t="n">
-        <v>370.51</v>
-      </c>
-      <c r="F22" t="n">
-        <v>370.51</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-6.21</v>
-      </c>
-      <c r="H22" t="n">
-        <v>395.04</v>
-      </c>
-      <c r="I22" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:41:46</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>388.46</v>
-      </c>
-      <c r="D23" t="n">
-        <v>455.39</v>
-      </c>
-      <c r="E23" t="n">
-        <v>388.46</v>
-      </c>
-      <c r="F23" t="n">
-        <v>455.39</v>
-      </c>
-      <c r="G23" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="H23" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I23" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:41:46</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>386.23</v>
-      </c>
-      <c r="D24" t="n">
-        <v>446.48</v>
-      </c>
-      <c r="E24" t="n">
-        <v>386.23</v>
-      </c>
-      <c r="F24" t="n">
-        <v>446.48</v>
-      </c>
-      <c r="G24" t="n">
-        <v>22</v>
-      </c>
-      <c r="H24" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I24" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:41:46</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>384.01</v>
-      </c>
-      <c r="D25" t="n">
-        <v>438.41</v>
-      </c>
-      <c r="E25" t="n">
-        <v>384.01</v>
-      </c>
-      <c r="F25" t="n">
-        <v>438.41</v>
-      </c>
-      <c r="G25" t="n">
-        <v>19.79</v>
-      </c>
-      <c r="H25" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I25" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:46:20</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>365.54</v>
-      </c>
-      <c r="D26" t="n">
-        <v>382.93</v>
-      </c>
-      <c r="E26" t="n">
-        <v>365.54</v>
-      </c>
-      <c r="F26" t="n">
-        <v>382.93</v>
-      </c>
-      <c r="G26" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="H26" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I26" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:46:20</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>363.44</v>
-      </c>
-      <c r="D27" t="n">
-        <v>375.44</v>
-      </c>
-      <c r="E27" t="n">
-        <v>363.44</v>
-      </c>
-      <c r="F27" t="n">
-        <v>375.44</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="H27" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I27" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:46:20</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>361.35</v>
-      </c>
-      <c r="D28" t="n">
-        <v>374.61</v>
-      </c>
-      <c r="E28" t="n">
-        <v>361.35</v>
-      </c>
-      <c r="F28" t="n">
-        <v>368.66</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="H28" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I28" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:50:22</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>401.16</v>
-      </c>
-      <c r="D29" t="n">
-        <v>414.18</v>
-      </c>
-      <c r="E29" t="n">
-        <v>396.7</v>
-      </c>
-      <c r="F29" t="n">
-        <v>396.7</v>
-      </c>
-      <c r="G29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I29" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:50:22</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>398.86</v>
-      </c>
-      <c r="D30" t="n">
-        <v>410.69</v>
-      </c>
-      <c r="E30" t="n">
-        <v>388.94</v>
-      </c>
-      <c r="F30" t="n">
-        <v>388.94</v>
-      </c>
-      <c r="G30" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="H30" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I30" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-03-27 23:50:22</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>396.56</v>
-      </c>
-      <c r="D31" t="n">
-        <v>406.08</v>
-      </c>
-      <c r="E31" t="n">
-        <v>381.92</v>
-      </c>
-      <c r="F31" t="n">
-        <v>381.92</v>
-      </c>
-      <c r="G31" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="H31" t="n">
-        <v>365.97</v>
-      </c>
-      <c r="I31" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2106,6 +2106,234 @@
       <c r="J43" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>634.96</v>
+      </c>
+      <c r="D44" t="n">
+        <v>673.78</v>
+      </c>
+      <c r="E44" t="n">
+        <v>634.96</v>
+      </c>
+      <c r="F44" t="n">
+        <v>673.78</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H44" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I44" t="n">
+        <v>80</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>630.02</v>
+      </c>
+      <c r="D45" t="n">
+        <v>656.01</v>
+      </c>
+      <c r="E45" t="n">
+        <v>630.02</v>
+      </c>
+      <c r="F45" t="n">
+        <v>654.3200000000001</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H45" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I45" t="n">
+        <v>80</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>625.09</v>
+      </c>
+      <c r="D46" t="n">
+        <v>649.47</v>
+      </c>
+      <c r="E46" t="n">
+        <v>625.09</v>
+      </c>
+      <c r="F46" t="n">
+        <v>639.9299999999999</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="H46" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I46" t="n">
+        <v>80</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>633.22</v>
+      </c>
+      <c r="D47" t="n">
+        <v>669.78</v>
+      </c>
+      <c r="E47" t="n">
+        <v>633.22</v>
+      </c>
+      <c r="F47" t="n">
+        <v>669.78</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H47" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I47" t="n">
+        <v>80</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>628.29</v>
+      </c>
+      <c r="D48" t="n">
+        <v>654.86</v>
+      </c>
+      <c r="E48" t="n">
+        <v>628.29</v>
+      </c>
+      <c r="F48" t="n">
+        <v>650.4299999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="H48" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I48" t="n">
+        <v>80</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>623.37</v>
+      </c>
+      <c r="D49" t="n">
+        <v>645.64</v>
+      </c>
+      <c r="E49" t="n">
+        <v>623.37</v>
+      </c>
+      <c r="F49" t="n">
+        <v>636.13</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="H49" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I49" t="n">
+        <v>80</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3798,6 +4026,234 @@
       <c r="J43" t="inlineStr">
         <is>
           <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>249.97</v>
+      </c>
+      <c r="D44" t="n">
+        <v>258.91</v>
+      </c>
+      <c r="E44" t="n">
+        <v>231.73</v>
+      </c>
+      <c r="F44" t="n">
+        <v>247.25</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-4.49</v>
+      </c>
+      <c r="H44" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I44" t="n">
+        <v>80</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>248.13</v>
+      </c>
+      <c r="D45" t="n">
+        <v>251.82</v>
+      </c>
+      <c r="E45" t="n">
+        <v>231.73</v>
+      </c>
+      <c r="F45" t="n">
+        <v>240.48</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I45" t="n">
+        <v>80</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>246.29</v>
+      </c>
+      <c r="D46" t="n">
+        <v>251.82</v>
+      </c>
+      <c r="E46" t="n">
+        <v>226.9</v>
+      </c>
+      <c r="F46" t="n">
+        <v>235.47</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-9.039999999999999</v>
+      </c>
+      <c r="H46" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I46" t="n">
+        <v>80</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>249.74</v>
+      </c>
+      <c r="D47" t="n">
+        <v>256.37</v>
+      </c>
+      <c r="E47" t="n">
+        <v>232.17</v>
+      </c>
+      <c r="F47" t="n">
+        <v>246.03</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="H47" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I47" t="n">
+        <v>80</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>247.9</v>
+      </c>
+      <c r="D48" t="n">
+        <v>249.35</v>
+      </c>
+      <c r="E48" t="n">
+        <v>232.17</v>
+      </c>
+      <c r="F48" t="n">
+        <v>239.29</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-7.56</v>
+      </c>
+      <c r="H48" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I48" t="n">
+        <v>80</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>246.06</v>
+      </c>
+      <c r="D49" t="n">
+        <v>249.35</v>
+      </c>
+      <c r="E49" t="n">
+        <v>227.34</v>
+      </c>
+      <c r="F49" t="n">
+        <v>234.31</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-9.48</v>
+      </c>
+      <c r="H49" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I49" t="n">
+        <v>80</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -3812,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5490,6 +5946,234 @@
       <c r="J43" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>351.61</v>
+      </c>
+      <c r="D44" t="n">
+        <v>381.18</v>
+      </c>
+      <c r="E44" t="n">
+        <v>324.97</v>
+      </c>
+      <c r="F44" t="n">
+        <v>324.97</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-12.85</v>
+      </c>
+      <c r="H44" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I44" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>348.44</v>
+      </c>
+      <c r="D45" t="n">
+        <v>368.47</v>
+      </c>
+      <c r="E45" t="n">
+        <v>314.13</v>
+      </c>
+      <c r="F45" t="n">
+        <v>314.13</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-15.75</v>
+      </c>
+      <c r="H45" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I45" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>345.27</v>
+      </c>
+      <c r="D46" t="n">
+        <v>368.47</v>
+      </c>
+      <c r="E46" t="n">
+        <v>306.12</v>
+      </c>
+      <c r="F46" t="n">
+        <v>306.12</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-17.9</v>
+      </c>
+      <c r="H46" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I46" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:19</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>374.42</v>
+      </c>
+      <c r="D47" t="n">
+        <v>438.78</v>
+      </c>
+      <c r="E47" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="F47" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="H47" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I47" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:19</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>371.04</v>
+      </c>
+      <c r="D48" t="n">
+        <v>424.14</v>
+      </c>
+      <c r="E48" t="n">
+        <v>358.02</v>
+      </c>
+      <c r="F48" t="n">
+        <v>358.02</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="H48" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I48" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="D49" t="n">
+        <v>424.14</v>
+      </c>
+      <c r="E49" t="n">
+        <v>348.89</v>
+      </c>
+      <c r="F49" t="n">
+        <v>348.89</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="H49" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I49" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -5504,7 +6188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5985,6 +6669,270 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>211.26</v>
+      </c>
+      <c r="D11" t="n">
+        <v>223.13</v>
+      </c>
+      <c r="E11" t="n">
+        <v>202.76</v>
+      </c>
+      <c r="F11" t="n">
+        <v>222.37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I11" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>208.62</v>
+      </c>
+      <c r="D12" t="n">
+        <v>212.91</v>
+      </c>
+      <c r="E12" t="n">
+        <v>202.76</v>
+      </c>
+      <c r="F12" t="n">
+        <v>212.19</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H12" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I12" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:40:24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>205.98</v>
+      </c>
+      <c r="D13" t="n">
+        <v>212.91</v>
+      </c>
+      <c r="E13" t="n">
+        <v>195.57</v>
+      </c>
+      <c r="F13" t="n">
+        <v>204.66</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="H13" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I13" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>234.26</v>
+      </c>
+      <c r="D14" t="n">
+        <v>240.82</v>
+      </c>
+      <c r="E14" t="n">
+        <v>224.97</v>
+      </c>
+      <c r="F14" t="n">
+        <v>238.37</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="H14" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I14" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>231.33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>231.33</v>
+      </c>
+      <c r="E15" t="n">
+        <v>224.97</v>
+      </c>
+      <c r="F15" t="n">
+        <v>227.45</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="H15" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I15" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-07 17:44:19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>229.79</v>
+      </c>
+      <c r="E16" t="n">
+        <v>216.99</v>
+      </c>
+      <c r="F16" t="n">
+        <v>219.38</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I16" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2332,6 +2332,120 @@
         <v>80</v>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>633.73</v>
+      </c>
+      <c r="D50" t="n">
+        <v>668.26</v>
+      </c>
+      <c r="E50" t="n">
+        <v>633.73</v>
+      </c>
+      <c r="F50" t="n">
+        <v>668.26</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H50" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I50" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>628.8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>654.3200000000001</v>
+      </c>
+      <c r="E51" t="n">
+        <v>628.8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>648.95</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="H51" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I51" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>623.87</v>
+      </c>
+      <c r="D52" t="n">
+        <v>644.3200000000001</v>
+      </c>
+      <c r="E52" t="n">
+        <v>623.87</v>
+      </c>
+      <c r="F52" t="n">
+        <v>634.6799999999999</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-3.68</v>
+      </c>
+      <c r="H52" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I52" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -2348,7 +2462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4254,6 +4368,120 @@
       <c r="J49" t="inlineStr">
         <is>
           <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>257.01</v>
+      </c>
+      <c r="D50" t="n">
+        <v>275.13</v>
+      </c>
+      <c r="E50" t="n">
+        <v>240.71</v>
+      </c>
+      <c r="F50" t="n">
+        <v>268.01</v>
+      </c>
+      <c r="G50" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H50" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I50" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>255.11</v>
+      </c>
+      <c r="D51" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="E51" t="n">
+        <v>240.71</v>
+      </c>
+      <c r="F51" t="n">
+        <v>260.67</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H51" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I51" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>253.22</v>
+      </c>
+      <c r="D52" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="E52" t="n">
+        <v>235.7</v>
+      </c>
+      <c r="F52" t="n">
+        <v>255.24</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I52" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6174,6 +6402,120 @@
       <c r="J49" t="inlineStr">
         <is>
           <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>353.78</v>
+      </c>
+      <c r="D50" t="n">
+        <v>428.04</v>
+      </c>
+      <c r="E50" t="n">
+        <v>353.78</v>
+      </c>
+      <c r="F50" t="n">
+        <v>355</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="H50" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I50" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>350.59</v>
+      </c>
+      <c r="D51" t="n">
+        <v>413.76</v>
+      </c>
+      <c r="E51" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="F51" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-7.97</v>
+      </c>
+      <c r="H51" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I51" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>347.4</v>
+      </c>
+      <c r="D52" t="n">
+        <v>413.76</v>
+      </c>
+      <c r="E52" t="n">
+        <v>334.4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>334.4</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-10.32</v>
+      </c>
+      <c r="H52" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I52" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6933,6 +7275,138 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>227.13</v>
+      </c>
+      <c r="D17" t="n">
+        <v>245.28</v>
+      </c>
+      <c r="E17" t="n">
+        <v>210.45</v>
+      </c>
+      <c r="F17" t="n">
+        <v>245.28</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="H17" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I17" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="D18" t="n">
+        <v>234.05</v>
+      </c>
+      <c r="E18" t="n">
+        <v>210.45</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234.05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H18" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I18" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:26:21</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>221.45</v>
+      </c>
+      <c r="D19" t="n">
+        <v>225.74</v>
+      </c>
+      <c r="E19" t="n">
+        <v>202.98</v>
+      </c>
+      <c r="F19" t="n">
+        <v>225.74</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="H19" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I19" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2446,6 +2446,120 @@
         <v>83.3</v>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>633.73</v>
+      </c>
+      <c r="D53" t="n">
+        <v>666.98</v>
+      </c>
+      <c r="E53" t="n">
+        <v>633.73</v>
+      </c>
+      <c r="F53" t="n">
+        <v>666.98</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H53" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I53" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>628.8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>654.01</v>
+      </c>
+      <c r="E54" t="n">
+        <v>628.8</v>
+      </c>
+      <c r="F54" t="n">
+        <v>647.71</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H54" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I54" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>623.87</v>
+      </c>
+      <c r="D55" t="n">
+        <v>643.46</v>
+      </c>
+      <c r="E55" t="n">
+        <v>623.87</v>
+      </c>
+      <c r="F55" t="n">
+        <v>633.47</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-3.86</v>
+      </c>
+      <c r="H55" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I55" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -2462,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4480,6 +4594,120 @@
         <v>83.3</v>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>256.63</v>
+      </c>
+      <c r="D53" t="n">
+        <v>275.13</v>
+      </c>
+      <c r="E53" t="n">
+        <v>240.06</v>
+      </c>
+      <c r="F53" t="n">
+        <v>268.46</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H53" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I53" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>254.74</v>
+      </c>
+      <c r="D54" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="E54" t="n">
+        <v>240.06</v>
+      </c>
+      <c r="F54" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H54" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I54" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>252.85</v>
+      </c>
+      <c r="D55" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>235.06</v>
+      </c>
+      <c r="F55" t="n">
+        <v>255.67</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="H55" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I55" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -4496,7 +4724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6516,6 +6744,120 @@
       <c r="J52" t="inlineStr">
         <is>
           <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>349.19</v>
+      </c>
+      <c r="D53" t="n">
+        <v>436.41</v>
+      </c>
+      <c r="E53" t="n">
+        <v>349.19</v>
+      </c>
+      <c r="F53" t="n">
+        <v>352.27</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="H53" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I53" t="n">
+        <v>80</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>346.04</v>
+      </c>
+      <c r="D54" t="n">
+        <v>421.85</v>
+      </c>
+      <c r="E54" t="n">
+        <v>340.52</v>
+      </c>
+      <c r="F54" t="n">
+        <v>340.52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="H54" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I54" t="n">
+        <v>80</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>342.89</v>
+      </c>
+      <c r="D55" t="n">
+        <v>421.85</v>
+      </c>
+      <c r="E55" t="n">
+        <v>331.83</v>
+      </c>
+      <c r="F55" t="n">
+        <v>331.83</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-11.01</v>
+      </c>
+      <c r="H55" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I55" t="n">
+        <v>80</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7407,6 +7749,138 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>227.55</v>
+      </c>
+      <c r="D20" t="n">
+        <v>246.59</v>
+      </c>
+      <c r="E20" t="n">
+        <v>210.65</v>
+      </c>
+      <c r="F20" t="n">
+        <v>246.59</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="H20" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I20" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>224.71</v>
+      </c>
+      <c r="D21" t="n">
+        <v>235.29</v>
+      </c>
+      <c r="E21" t="n">
+        <v>210.65</v>
+      </c>
+      <c r="F21" t="n">
+        <v>235.29</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="H21" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I21" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-07 18:29:45</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>221.87</v>
+      </c>
+      <c r="D22" t="n">
+        <v>226.94</v>
+      </c>
+      <c r="E22" t="n">
+        <v>203.18</v>
+      </c>
+      <c r="F22" t="n">
+        <v>226.94</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="H22" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I22" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2560,6 +2560,120 @@
         <v>83.3</v>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>633.66</v>
+      </c>
+      <c r="D56" t="n">
+        <v>666.03</v>
+      </c>
+      <c r="E56" t="n">
+        <v>633.66</v>
+      </c>
+      <c r="F56" t="n">
+        <v>666.03</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="H56" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I56" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>628.73</v>
+      </c>
+      <c r="D57" t="n">
+        <v>654.77</v>
+      </c>
+      <c r="E57" t="n">
+        <v>628.73</v>
+      </c>
+      <c r="F57" t="n">
+        <v>646.79</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="H57" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I57" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>623.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>643.13</v>
+      </c>
+      <c r="E58" t="n">
+        <v>623.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>632.5700000000001</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H58" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I58" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -2576,7 +2690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4708,6 +4822,120 @@
         <v>83.3</v>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="D56" t="n">
+        <v>275.47</v>
+      </c>
+      <c r="E56" t="n">
+        <v>240.41</v>
+      </c>
+      <c r="F56" t="n">
+        <v>268.89</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H56" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I56" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>254.91</v>
+      </c>
+      <c r="D57" t="n">
+        <v>267.92</v>
+      </c>
+      <c r="E57" t="n">
+        <v>240.41</v>
+      </c>
+      <c r="F57" t="n">
+        <v>261.53</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H57" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I57" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>253.02</v>
+      </c>
+      <c r="D58" t="n">
+        <v>267.92</v>
+      </c>
+      <c r="E58" t="n">
+        <v>235.4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>256.08</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="H58" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I58" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -4724,7 +4952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P55"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6858,6 +7086,120 @@
       <c r="J55" t="inlineStr">
         <is>
           <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>345.49</v>
+      </c>
+      <c r="D56" t="n">
+        <v>426.92</v>
+      </c>
+      <c r="E56" t="n">
+        <v>345.49</v>
+      </c>
+      <c r="F56" t="n">
+        <v>351.31</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="H56" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I56" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="D57" t="n">
+        <v>412.67</v>
+      </c>
+      <c r="E57" t="n">
+        <v>339.59</v>
+      </c>
+      <c r="F57" t="n">
+        <v>339.59</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-8.93</v>
+      </c>
+      <c r="H57" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I57" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:30</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>339.26</v>
+      </c>
+      <c r="D58" t="n">
+        <v>412.67</v>
+      </c>
+      <c r="E58" t="n">
+        <v>330.93</v>
+      </c>
+      <c r="F58" t="n">
+        <v>330.93</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-11.25</v>
+      </c>
+      <c r="H58" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I58" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>HOLD</t>
         </is>
       </c>
     </row>
@@ -6872,7 +7214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7881,6 +8223,138 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:31</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>226.28</v>
+      </c>
+      <c r="D23" t="n">
+        <v>245.54</v>
+      </c>
+      <c r="E23" t="n">
+        <v>210.67</v>
+      </c>
+      <c r="F23" t="n">
+        <v>245.54</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="H23" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I23" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>223.46</v>
+      </c>
+      <c r="D24" t="n">
+        <v>234.3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>210.67</v>
+      </c>
+      <c r="F24" t="n">
+        <v>234.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="H24" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I24" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-07 19:37:31</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>220.63</v>
+      </c>
+      <c r="D25" t="n">
+        <v>225.98</v>
+      </c>
+      <c r="E25" t="n">
+        <v>203.19</v>
+      </c>
+      <c r="F25" t="n">
+        <v>225.98</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I25" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2674,6 +2674,120 @@
         <v>83.3</v>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>633.35</v>
+      </c>
+      <c r="D59" t="n">
+        <v>665.51</v>
+      </c>
+      <c r="E59" t="n">
+        <v>633.35</v>
+      </c>
+      <c r="F59" t="n">
+        <v>665.51</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I59" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>628.42</v>
+      </c>
+      <c r="D60" t="n">
+        <v>654.92</v>
+      </c>
+      <c r="E60" t="n">
+        <v>628.42</v>
+      </c>
+      <c r="F60" t="n">
+        <v>646.28</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="H60" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I60" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>623.5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>643.21</v>
+      </c>
+      <c r="E61" t="n">
+        <v>623.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>632.0700000000001</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="H61" t="n">
+        <v>658.9299999999999</v>
+      </c>
+      <c r="I61" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -2690,7 +2804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4936,6 +5050,120 @@
         <v>83.3</v>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>256.96</v>
+      </c>
+      <c r="D59" t="n">
+        <v>275.21</v>
+      </c>
+      <c r="E59" t="n">
+        <v>240.24</v>
+      </c>
+      <c r="F59" t="n">
+        <v>269.71</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="H59" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I59" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>255.06</v>
+      </c>
+      <c r="D60" t="n">
+        <v>267.67</v>
+      </c>
+      <c r="E60" t="n">
+        <v>240.24</v>
+      </c>
+      <c r="F60" t="n">
+        <v>262.33</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="H60" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I60" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>253.17</v>
+      </c>
+      <c r="D61" t="n">
+        <v>267.67</v>
+      </c>
+      <c r="E61" t="n">
+        <v>235.24</v>
+      </c>
+      <c r="F61" t="n">
+        <v>256.87</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="H61" t="n">
+        <v>258.86</v>
+      </c>
+      <c r="I61" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -4952,7 +5180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7198,6 +7426,120 @@
         <v>81.7</v>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="D59" t="n">
+        <v>426.48</v>
+      </c>
+      <c r="E59" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="F59" t="n">
+        <v>350.04</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="H59" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I59" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>340.47</v>
+      </c>
+      <c r="D60" t="n">
+        <v>412.25</v>
+      </c>
+      <c r="E60" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="F60" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="H60" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I60" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:11</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="D61" t="n">
+        <v>412.25</v>
+      </c>
+      <c r="E61" t="n">
+        <v>329.73</v>
+      </c>
+      <c r="F61" t="n">
+        <v>329.73</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-11.57</v>
+      </c>
+      <c r="H61" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="I61" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
@@ -7214,7 +7556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8355,6 +8697,138 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:12</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>225.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>245.88</v>
+      </c>
+      <c r="E26" t="n">
+        <v>210.89</v>
+      </c>
+      <c r="F26" t="n">
+        <v>245.88</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="H26" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I26" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:12</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>222.98</v>
+      </c>
+      <c r="D27" t="n">
+        <v>234.62</v>
+      </c>
+      <c r="E27" t="n">
+        <v>210.89</v>
+      </c>
+      <c r="F27" t="n">
+        <v>234.62</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="H27" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I27" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-07 20:17:12</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>220.16</v>
+      </c>
+      <c r="D28" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="E28" t="n">
+        <v>203.4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>226.29</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="H28" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="I28" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3157,6 +3157,234 @@
         <v>83.3</v>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>638.91</v>
+      </c>
+      <c r="D71" t="n">
+        <v>661.97</v>
+      </c>
+      <c r="E71" t="n">
+        <v>638.91</v>
+      </c>
+      <c r="F71" t="n">
+        <v>658.66</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H71" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I71" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:04</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>633.8200000000001</v>
+      </c>
+      <c r="D72" t="n">
+        <v>642.42</v>
+      </c>
+      <c r="E72" t="n">
+        <v>633.8200000000001</v>
+      </c>
+      <c r="F72" t="n">
+        <v>639.21</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="H72" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I72" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:04</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>628.74</v>
+      </c>
+      <c r="D73" t="n">
+        <v>642.42</v>
+      </c>
+      <c r="E73" t="n">
+        <v>624.83</v>
+      </c>
+      <c r="F73" t="n">
+        <v>624.83</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="H73" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I73" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>638.8200000000001</v>
+      </c>
+      <c r="D74" t="n">
+        <v>662.84</v>
+      </c>
+      <c r="E74" t="n">
+        <v>638.8200000000001</v>
+      </c>
+      <c r="F74" t="n">
+        <v>659.35</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H74" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I74" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>633.74</v>
+      </c>
+      <c r="D75" t="n">
+        <v>643.26</v>
+      </c>
+      <c r="E75" t="n">
+        <v>633.74</v>
+      </c>
+      <c r="F75" t="n">
+        <v>639.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="H75" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I75" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>628.66</v>
+      </c>
+      <c r="D76" t="n">
+        <v>643.26</v>
+      </c>
+      <c r="E76" t="n">
+        <v>625.11</v>
+      </c>
+      <c r="F76" t="n">
+        <v>625.49</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="H76" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I76" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -3173,7 +3401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5845,6 +6073,234 @@
         <v>81.7</v>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:04</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>265.66</v>
+      </c>
+      <c r="D71" t="n">
+        <v>272.85</v>
+      </c>
+      <c r="E71" t="n">
+        <v>244.62</v>
+      </c>
+      <c r="F71" t="n">
+        <v>265.72</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H71" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I71" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:04</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>263.46</v>
+      </c>
+      <c r="D72" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="E72" t="n">
+        <v>244.62</v>
+      </c>
+      <c r="F72" t="n">
+        <v>257.52</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H72" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I72" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:04</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>261.25</v>
+      </c>
+      <c r="D73" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="E73" t="n">
+        <v>238.87</v>
+      </c>
+      <c r="F73" t="n">
+        <v>251.47</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H73" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>265.73</v>
+      </c>
+      <c r="D74" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>244.13</v>
+      </c>
+      <c r="F74" t="n">
+        <v>265.72</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="H74" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>263.52</v>
+      </c>
+      <c r="D75" t="n">
+        <v>264</v>
+      </c>
+      <c r="E75" t="n">
+        <v>244.13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>257.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H75" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>261.31</v>
+      </c>
+      <c r="D76" t="n">
+        <v>264</v>
+      </c>
+      <c r="E76" t="n">
+        <v>238.38</v>
+      </c>
+      <c r="F76" t="n">
+        <v>251.47</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="H76" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -5861,7 +6317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8535,6 +8991,234 @@
       <c r="J70" t="inlineStr">
         <is>
           <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="D71" t="n">
+        <v>444.89</v>
+      </c>
+      <c r="E71" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="F71" t="n">
+        <v>392.59</v>
+      </c>
+      <c r="G71" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="H71" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I71" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>336.55</v>
+      </c>
+      <c r="D72" t="n">
+        <v>429.97</v>
+      </c>
+      <c r="E72" t="n">
+        <v>336.55</v>
+      </c>
+      <c r="F72" t="n">
+        <v>379.42</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H72" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I72" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>333.47</v>
+      </c>
+      <c r="D73" t="n">
+        <v>429.97</v>
+      </c>
+      <c r="E73" t="n">
+        <v>333.47</v>
+      </c>
+      <c r="F73" t="n">
+        <v>369.69</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="H73" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I73" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>339.06</v>
+      </c>
+      <c r="D74" t="n">
+        <v>441.29</v>
+      </c>
+      <c r="E74" t="n">
+        <v>339.06</v>
+      </c>
+      <c r="F74" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="G74" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="H74" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I74" t="n">
+        <v>85</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>335.99</v>
+      </c>
+      <c r="D75" t="n">
+        <v>426.48</v>
+      </c>
+      <c r="E75" t="n">
+        <v>335.99</v>
+      </c>
+      <c r="F75" t="n">
+        <v>380.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H75" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I75" t="n">
+        <v>85</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:18</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>332.91</v>
+      </c>
+      <c r="D76" t="n">
+        <v>426.48</v>
+      </c>
+      <c r="E76" t="n">
+        <v>332.91</v>
+      </c>
+      <c r="F76" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I76" t="n">
+        <v>85</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
@@ -8549,7 +9233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9967,6 +10651,234 @@
         <v>85</v>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>220.51</v>
+      </c>
+      <c r="D38" t="n">
+        <v>236.57</v>
+      </c>
+      <c r="E38" t="n">
+        <v>215.8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>236.57</v>
+      </c>
+      <c r="G38" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="H38" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I38" t="n">
+        <v>85</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>217.95</v>
+      </c>
+      <c r="D39" t="n">
+        <v>226.46</v>
+      </c>
+      <c r="E39" t="n">
+        <v>215.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>226.46</v>
+      </c>
+      <c r="G39" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="H39" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I39" t="n">
+        <v>85</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>215.39</v>
+      </c>
+      <c r="D40" t="n">
+        <v>220.62</v>
+      </c>
+      <c r="E40" t="n">
+        <v>208.68</v>
+      </c>
+      <c r="F40" t="n">
+        <v>218.99</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H40" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I40" t="n">
+        <v>85</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>220.49</v>
+      </c>
+      <c r="D41" t="n">
+        <v>236.46</v>
+      </c>
+      <c r="E41" t="n">
+        <v>215.97</v>
+      </c>
+      <c r="F41" t="n">
+        <v>236.46</v>
+      </c>
+      <c r="G41" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="H41" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I41" t="n">
+        <v>85</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>217.93</v>
+      </c>
+      <c r="D42" t="n">
+        <v>226.36</v>
+      </c>
+      <c r="E42" t="n">
+        <v>215.97</v>
+      </c>
+      <c r="F42" t="n">
+        <v>226.36</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="H42" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I42" t="n">
+        <v>85</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:19</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>215.37</v>
+      </c>
+      <c r="D43" t="n">
+        <v>220.77</v>
+      </c>
+      <c r="E43" t="n">
+        <v>208.85</v>
+      </c>
+      <c r="F43" t="n">
+        <v>218.89</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I43" t="n">
+        <v>85</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -9983,7 +10895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10380,6 +11292,234 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>610.62</v>
+      </c>
+      <c r="D11" t="n">
+        <v>689.89</v>
+      </c>
+      <c r="E11" t="n">
+        <v>590.33</v>
+      </c>
+      <c r="F11" t="n">
+        <v>689.89</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="H11" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I11" t="n">
+        <v>80</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>597.95</v>
+      </c>
+      <c r="D12" t="n">
+        <v>638.55</v>
+      </c>
+      <c r="E12" t="n">
+        <v>590.33</v>
+      </c>
+      <c r="F12" t="n">
+        <v>638.55</v>
+      </c>
+      <c r="G12" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="H12" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I12" t="n">
+        <v>80</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-08 16:52:05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>585.28</v>
+      </c>
+      <c r="D13" t="n">
+        <v>638.54</v>
+      </c>
+      <c r="E13" t="n">
+        <v>555.25</v>
+      </c>
+      <c r="F13" t="n">
+        <v>600.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="H13" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I13" t="n">
+        <v>80</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>611.11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>689.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>589.63</v>
+      </c>
+      <c r="F14" t="n">
+        <v>689.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="H14" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I14" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>598.4299999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>637.8200000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>589.63</v>
+      </c>
+      <c r="F15" t="n">
+        <v>637.8200000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="H15" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I15" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-08 17:09:19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>585.76</v>
+      </c>
+      <c r="D16" t="n">
+        <v>636.25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>554.59</v>
+      </c>
+      <c r="F16" t="n">
+        <v>599.92</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="H16" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I16" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3385,6 +3385,120 @@
         <v>83.3</v>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>638.8200000000001</v>
+      </c>
+      <c r="D77" t="n">
+        <v>663.02</v>
+      </c>
+      <c r="E77" t="n">
+        <v>638.8200000000001</v>
+      </c>
+      <c r="F77" t="n">
+        <v>659.4</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H77" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I77" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>633.74</v>
+      </c>
+      <c r="D78" t="n">
+        <v>643.4400000000001</v>
+      </c>
+      <c r="E78" t="n">
+        <v>633.74</v>
+      </c>
+      <c r="F78" t="n">
+        <v>639.9299999999999</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="H78" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I78" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>628.66</v>
+      </c>
+      <c r="D79" t="n">
+        <v>643.4400000000001</v>
+      </c>
+      <c r="E79" t="n">
+        <v>625.02</v>
+      </c>
+      <c r="F79" t="n">
+        <v>625.54</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="H79" t="n">
+        <v>659.22</v>
+      </c>
+      <c r="I79" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>BUY</t>
         </is>
@@ -3401,7 +3515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6301,6 +6415,120 @@
         <v>83.3</v>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>265.89</v>
+      </c>
+      <c r="D77" t="n">
+        <v>272.25</v>
+      </c>
+      <c r="E77" t="n">
+        <v>243.83</v>
+      </c>
+      <c r="F77" t="n">
+        <v>265.59</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H77" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I77" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>263.68</v>
+      </c>
+      <c r="D78" t="n">
+        <v>263.86</v>
+      </c>
+      <c r="E78" t="n">
+        <v>243.83</v>
+      </c>
+      <c r="F78" t="n">
+        <v>257.4</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H78" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I78" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>261.47</v>
+      </c>
+      <c r="D79" t="n">
+        <v>263.86</v>
+      </c>
+      <c r="E79" t="n">
+        <v>238.1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>251.35</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="H79" t="n">
+        <v>253.5</v>
+      </c>
+      <c r="I79" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -6317,7 +6545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9217,6 +9445,120 @@
         <v>85</v>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>338.32</v>
+      </c>
+      <c r="D77" t="n">
+        <v>440.41</v>
+      </c>
+      <c r="E77" t="n">
+        <v>338.32</v>
+      </c>
+      <c r="F77" t="n">
+        <v>394.18</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="H77" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I77" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="D78" t="n">
+        <v>425.63</v>
+      </c>
+      <c r="E78" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="F78" t="n">
+        <v>380.96</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="H78" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I78" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:03</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>332.19</v>
+      </c>
+      <c r="D79" t="n">
+        <v>425.63</v>
+      </c>
+      <c r="E79" t="n">
+        <v>332.19</v>
+      </c>
+      <c r="F79" t="n">
+        <v>371.19</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H79" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="I79" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -9233,7 +9575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10879,6 +11221,120 @@
         <v>85</v>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>220.52</v>
+      </c>
+      <c r="D44" t="n">
+        <v>236.42</v>
+      </c>
+      <c r="E44" t="n">
+        <v>215.98</v>
+      </c>
+      <c r="F44" t="n">
+        <v>236.42</v>
+      </c>
+      <c r="G44" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H44" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I44" t="n">
+        <v>85</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>217.96</v>
+      </c>
+      <c r="D45" t="n">
+        <v>226.32</v>
+      </c>
+      <c r="E45" t="n">
+        <v>215.98</v>
+      </c>
+      <c r="F45" t="n">
+        <v>226.32</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H45" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I45" t="n">
+        <v>85</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>215.39</v>
+      </c>
+      <c r="D46" t="n">
+        <v>220.93</v>
+      </c>
+      <c r="E46" t="n">
+        <v>208.86</v>
+      </c>
+      <c r="F46" t="n">
+        <v>218.85</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H46" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="I46" t="n">
+        <v>85</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -10895,7 +11351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11520,6 +11976,120 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>611.08</v>
+      </c>
+      <c r="D17" t="n">
+        <v>688.99</v>
+      </c>
+      <c r="E17" t="n">
+        <v>589.63</v>
+      </c>
+      <c r="F17" t="n">
+        <v>688.99</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="H17" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I17" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>598.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>637.72</v>
+      </c>
+      <c r="E18" t="n">
+        <v>589.63</v>
+      </c>
+      <c r="F18" t="n">
+        <v>637.72</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I18" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:12:04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>585.72</v>
+      </c>
+      <c r="D19" t="n">
+        <v>635.85</v>
+      </c>
+      <c r="E19" t="n">
+        <v>554.59</v>
+      </c>
+      <c r="F19" t="n">
+        <v>599.8200000000001</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="H19" t="n">
+        <v>575.05</v>
+      </c>
+      <c r="I19" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="SPY"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="58">
   <si>
     <t>Exported At</t>
   </si>
@@ -228,7 +228,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -258,11 +258,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -287,6 +302,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8825,7 +8846,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
@@ -8841,35 +8862,35 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4">
-        <v>200.6</v>
-      </c>
-      <c r="D1" s="4">
-        <v>237.66</v>
-      </c>
-      <c r="E1" s="4">
-        <v>200.6</v>
-      </c>
-      <c r="F1" s="4">
-        <v>223.48</v>
-      </c>
-      <c r="G1" s="4">
-        <v>11.41</v>
-      </c>
-      <c r="H1" s="4">
-        <v>200.59</v>
-      </c>
-      <c r="I1" s="4">
-        <v>76.7</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>23</v>
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
@@ -8877,22 +8898,22 @@
         <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4">
-        <v>198.51</v>
+        <v>200.6</v>
       </c>
       <c r="D2" s="4">
-        <v>230.07</v>
+        <v>237.66</v>
       </c>
       <c r="E2" s="4">
-        <v>198.51</v>
+        <v>200.6</v>
       </c>
       <c r="F2" s="4">
-        <v>216.34</v>
+        <v>223.48</v>
       </c>
       <c r="G2" s="4">
-        <v>7.85</v>
+        <v>11.41</v>
       </c>
       <c r="H2" s="4">
         <v>200.59</v>
@@ -8909,22 +8930,22 @@
         <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" s="4">
-        <v>196.42</v>
+        <v>198.51</v>
       </c>
       <c r="D3" s="4">
         <v>230.07</v>
       </c>
       <c r="E3" s="4">
-        <v>196.42</v>
+        <v>198.51</v>
       </c>
       <c r="F3" s="4">
-        <v>208.45</v>
+        <v>216.34</v>
       </c>
       <c r="G3" s="4">
-        <v>3.92</v>
+        <v>7.85</v>
       </c>
       <c r="H3" s="4">
         <v>200.59</v>
@@ -8938,28 +8959,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4">
-        <v>199.04</v>
+        <v>196.42</v>
       </c>
       <c r="D4" s="4">
-        <v>246.65</v>
+        <v>230.07</v>
       </c>
       <c r="E4" s="4">
-        <v>199.04</v>
+        <v>196.42</v>
       </c>
       <c r="F4" s="4">
-        <v>236.27</v>
+        <v>208.45</v>
       </c>
       <c r="G4" s="4">
-        <v>17.64</v>
+        <v>3.92</v>
       </c>
       <c r="H4" s="4">
-        <v>200.84</v>
+        <v>200.59</v>
       </c>
       <c r="I4" s="4">
         <v>76.7</v>
@@ -8973,22 +8994,22 @@
         <v>24</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4">
-        <v>196.97</v>
+        <v>199.04</v>
       </c>
       <c r="D5" s="4">
-        <v>238.8</v>
+        <v>246.65</v>
       </c>
       <c r="E5" s="4">
-        <v>196.97</v>
+        <v>199.04</v>
       </c>
       <c r="F5" s="4">
-        <v>228.75</v>
+        <v>236.27</v>
       </c>
       <c r="G5" s="4">
-        <v>13.89</v>
+        <v>17.64</v>
       </c>
       <c r="H5" s="4">
         <v>200.84</v>
@@ -9005,22 +9026,22 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4">
-        <v>194.9</v>
+        <v>196.97</v>
       </c>
       <c r="D6" s="4">
         <v>238.8</v>
       </c>
       <c r="E6" s="4">
-        <v>194.9</v>
+        <v>196.97</v>
       </c>
       <c r="F6" s="4">
-        <v>220.43</v>
+        <v>228.75</v>
       </c>
       <c r="G6" s="4">
-        <v>9.75</v>
+        <v>13.89</v>
       </c>
       <c r="H6" s="4">
         <v>200.84</v>
@@ -9034,28 +9055,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4">
-        <v>201.1</v>
+        <v>194.9</v>
       </c>
       <c r="D7" s="4">
-        <v>237.66</v>
+        <v>238.8</v>
       </c>
       <c r="E7" s="4">
-        <v>201.1</v>
+        <v>194.9</v>
       </c>
       <c r="F7" s="4">
-        <v>222.93</v>
+        <v>220.43</v>
       </c>
       <c r="G7" s="4">
-        <v>11.09</v>
+        <v>9.75</v>
       </c>
       <c r="H7" s="4">
-        <v>200.67</v>
+        <v>200.84</v>
       </c>
       <c r="I7" s="4">
         <v>76.7</v>
@@ -9069,22 +9090,22 @@
         <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4">
-        <v>199.01</v>
+        <v>201.1</v>
       </c>
       <c r="D8" s="4">
-        <v>230.08</v>
+        <v>237.66</v>
       </c>
       <c r="E8" s="4">
-        <v>199.01</v>
+        <v>201.1</v>
       </c>
       <c r="F8" s="4">
-        <v>215.82</v>
+        <v>222.93</v>
       </c>
       <c r="G8" s="4">
-        <v>7.55</v>
+        <v>11.09</v>
       </c>
       <c r="H8" s="4">
         <v>200.67</v>
@@ -9101,22 +9122,22 @@
         <v>25</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" s="4">
-        <v>196.92</v>
+        <v>199.01</v>
       </c>
       <c r="D9" s="4">
         <v>230.08</v>
       </c>
       <c r="E9" s="4">
-        <v>196.92</v>
+        <v>199.01</v>
       </c>
       <c r="F9" s="4">
-        <v>207.96</v>
+        <v>215.82</v>
       </c>
       <c r="G9" s="4">
-        <v>3.63</v>
+        <v>7.55</v>
       </c>
       <c r="H9" s="4">
         <v>200.67</v>
@@ -9130,34 +9151,34 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" s="4">
-        <v>211.26</v>
+        <v>196.92</v>
       </c>
       <c r="D10" s="4">
-        <v>223.13</v>
+        <v>230.08</v>
       </c>
       <c r="E10" s="4">
-        <v>202.76</v>
+        <v>196.92</v>
       </c>
       <c r="F10" s="4">
-        <v>222.37</v>
+        <v>207.96</v>
       </c>
       <c r="G10" s="4">
-        <v>4.5</v>
+        <v>3.63</v>
       </c>
       <c r="H10" s="4">
-        <v>212.79</v>
+        <v>200.67</v>
       </c>
       <c r="I10" s="4">
-        <v>78.3</v>
+        <v>76.7</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -9165,22 +9186,22 @@
         <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4">
-        <v>208.62</v>
+        <v>211.26</v>
       </c>
       <c r="D11" s="4">
-        <v>212.91</v>
+        <v>223.13</v>
       </c>
       <c r="E11" s="4">
         <v>202.76</v>
       </c>
       <c r="F11" s="4">
-        <v>212.19</v>
+        <v>222.37</v>
       </c>
       <c r="G11" s="4">
-        <v>-0.28</v>
+        <v>4.5</v>
       </c>
       <c r="H11" s="4">
         <v>212.79</v>
@@ -9197,22 +9218,22 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>205.98</v>
+        <v>208.62</v>
       </c>
       <c r="D12" s="4">
         <v>212.91</v>
       </c>
       <c r="E12" s="4">
-        <v>195.57</v>
+        <v>202.76</v>
       </c>
       <c r="F12" s="4">
-        <v>204.66</v>
+        <v>212.19</v>
       </c>
       <c r="G12" s="4">
-        <v>-3.82</v>
+        <v>-0.28</v>
       </c>
       <c r="H12" s="4">
         <v>212.79</v>
@@ -9226,25 +9247,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" s="4">
-        <v>234.26</v>
+        <v>205.98</v>
       </c>
       <c r="D13" s="4">
-        <v>240.82</v>
+        <v>212.91</v>
       </c>
       <c r="E13" s="4">
-        <v>224.97</v>
+        <v>195.57</v>
       </c>
       <c r="F13" s="4">
-        <v>238.37</v>
+        <v>204.66</v>
       </c>
       <c r="G13" s="4">
-        <v>12.02</v>
+        <v>-3.82</v>
       </c>
       <c r="H13" s="4">
         <v>212.79</v>
@@ -9261,22 +9282,22 @@
         <v>27</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" s="4">
-        <v>231.33</v>
+        <v>234.26</v>
       </c>
       <c r="D14" s="4">
-        <v>231.33</v>
+        <v>240.82</v>
       </c>
       <c r="E14" s="4">
         <v>224.97</v>
       </c>
       <c r="F14" s="4">
-        <v>227.45</v>
+        <v>238.37</v>
       </c>
       <c r="G14" s="4">
-        <v>6.89</v>
+        <v>12.02</v>
       </c>
       <c r="H14" s="4">
         <v>212.79</v>
@@ -9293,22 +9314,22 @@
         <v>27</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="4">
-        <v>228.4</v>
+        <v>231.33</v>
       </c>
       <c r="D15" s="4">
-        <v>229.79</v>
+        <v>231.33</v>
       </c>
       <c r="E15" s="4">
-        <v>216.99</v>
+        <v>224.97</v>
       </c>
       <c r="F15" s="4">
-        <v>219.38</v>
+        <v>227.45</v>
       </c>
       <c r="G15" s="4">
-        <v>3.1</v>
+        <v>6.89</v>
       </c>
       <c r="H15" s="4">
         <v>212.79</v>
@@ -9322,31 +9343,31 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" s="4">
-        <v>227.13</v>
+        <v>228.4</v>
       </c>
       <c r="D16" s="4">
-        <v>245.28</v>
+        <v>229.79</v>
       </c>
       <c r="E16" s="4">
-        <v>210.45</v>
+        <v>216.99</v>
       </c>
       <c r="F16" s="4">
-        <v>245.28</v>
+        <v>219.38</v>
       </c>
       <c r="G16" s="4">
-        <v>15.27</v>
+        <v>3.1</v>
       </c>
       <c r="H16" s="4">
         <v>212.79</v>
       </c>
       <c r="I16" s="4">
-        <v>81.7</v>
+        <v>78.3</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>12</v>
@@ -9357,22 +9378,22 @@
         <v>28</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" s="4">
-        <v>224.29</v>
+        <v>227.13</v>
       </c>
       <c r="D17" s="4">
-        <v>234.05</v>
+        <v>245.28</v>
       </c>
       <c r="E17" s="4">
         <v>210.45</v>
       </c>
       <c r="F17" s="4">
-        <v>234.05</v>
+        <v>245.28</v>
       </c>
       <c r="G17" s="4">
-        <v>9.99</v>
+        <v>15.27</v>
       </c>
       <c r="H17" s="4">
         <v>212.79</v>
@@ -9389,22 +9410,22 @@
         <v>28</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="4">
-        <v>221.45</v>
+        <v>224.29</v>
       </c>
       <c r="D18" s="4">
-        <v>225.74</v>
+        <v>234.05</v>
       </c>
       <c r="E18" s="4">
-        <v>202.98</v>
+        <v>210.45</v>
       </c>
       <c r="F18" s="4">
-        <v>225.74</v>
+        <v>234.05</v>
       </c>
       <c r="G18" s="4">
-        <v>6.09</v>
+        <v>9.99</v>
       </c>
       <c r="H18" s="4">
         <v>212.79</v>
@@ -9418,25 +9439,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" s="4">
-        <v>227.55</v>
+        <v>221.45</v>
       </c>
       <c r="D19" s="4">
-        <v>246.59</v>
+        <v>225.74</v>
       </c>
       <c r="E19" s="4">
-        <v>210.65</v>
+        <v>202.98</v>
       </c>
       <c r="F19" s="4">
-        <v>246.59</v>
+        <v>225.74</v>
       </c>
       <c r="G19" s="4">
-        <v>15.88</v>
+        <v>6.09</v>
       </c>
       <c r="H19" s="4">
         <v>212.79</v>
@@ -9453,22 +9474,22 @@
         <v>29</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C20" s="4">
-        <v>224.71</v>
+        <v>227.55</v>
       </c>
       <c r="D20" s="4">
-        <v>235.29</v>
+        <v>246.59</v>
       </c>
       <c r="E20" s="4">
         <v>210.65</v>
       </c>
       <c r="F20" s="4">
-        <v>235.29</v>
+        <v>246.59</v>
       </c>
       <c r="G20" s="4">
-        <v>10.57</v>
+        <v>15.88</v>
       </c>
       <c r="H20" s="4">
         <v>212.79</v>
@@ -9485,22 +9506,22 @@
         <v>29</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C21" s="4">
-        <v>221.87</v>
+        <v>224.71</v>
       </c>
       <c r="D21" s="4">
-        <v>226.94</v>
+        <v>235.29</v>
       </c>
       <c r="E21" s="4">
-        <v>203.18</v>
+        <v>210.65</v>
       </c>
       <c r="F21" s="4">
-        <v>226.94</v>
+        <v>235.29</v>
       </c>
       <c r="G21" s="4">
-        <v>6.65</v>
+        <v>10.57</v>
       </c>
       <c r="H21" s="4">
         <v>212.79</v>
@@ -9514,31 +9535,31 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" s="4">
-        <v>226.28</v>
+        <v>221.87</v>
       </c>
       <c r="D22" s="4">
-        <v>245.54</v>
+        <v>226.94</v>
       </c>
       <c r="E22" s="4">
-        <v>210.67</v>
+        <v>203.18</v>
       </c>
       <c r="F22" s="4">
-        <v>245.54</v>
+        <v>226.94</v>
       </c>
       <c r="G22" s="4">
-        <v>15.39</v>
+        <v>6.65</v>
       </c>
       <c r="H22" s="4">
         <v>212.79</v>
       </c>
       <c r="I22" s="4">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>12</v>
@@ -9549,22 +9570,22 @@
         <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C23" s="4">
-        <v>223.46</v>
+        <v>226.28</v>
       </c>
       <c r="D23" s="4">
-        <v>234.3</v>
+        <v>245.54</v>
       </c>
       <c r="E23" s="4">
         <v>210.67</v>
       </c>
       <c r="F23" s="4">
-        <v>234.3</v>
+        <v>245.54</v>
       </c>
       <c r="G23" s="4">
-        <v>10.11</v>
+        <v>15.39</v>
       </c>
       <c r="H23" s="4">
         <v>212.79</v>
@@ -9581,22 +9602,22 @@
         <v>30</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="4">
-        <v>220.63</v>
+        <v>223.46</v>
       </c>
       <c r="D24" s="4">
-        <v>225.98</v>
+        <v>234.3</v>
       </c>
       <c r="E24" s="4">
-        <v>203.19</v>
+        <v>210.67</v>
       </c>
       <c r="F24" s="4">
-        <v>225.98</v>
+        <v>234.3</v>
       </c>
       <c r="G24" s="4">
-        <v>6.2</v>
+        <v>10.11</v>
       </c>
       <c r="H24" s="4">
         <v>212.79</v>
@@ -9610,25 +9631,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" s="4">
-        <v>225.8</v>
+        <v>220.63</v>
       </c>
       <c r="D25" s="4">
-        <v>245.88</v>
+        <v>225.98</v>
       </c>
       <c r="E25" s="4">
-        <v>210.89</v>
+        <v>203.19</v>
       </c>
       <c r="F25" s="4">
-        <v>245.88</v>
+        <v>225.98</v>
       </c>
       <c r="G25" s="4">
-        <v>15.55</v>
+        <v>6.2</v>
       </c>
       <c r="H25" s="4">
         <v>212.79</v>
@@ -9645,22 +9666,22 @@
         <v>31</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C26" s="4">
-        <v>222.98</v>
+        <v>225.8</v>
       </c>
       <c r="D26" s="4">
-        <v>234.62</v>
+        <v>245.88</v>
       </c>
       <c r="E26" s="4">
         <v>210.89</v>
       </c>
       <c r="F26" s="4">
-        <v>234.62</v>
+        <v>245.88</v>
       </c>
       <c r="G26" s="4">
-        <v>10.26</v>
+        <v>15.55</v>
       </c>
       <c r="H26" s="4">
         <v>212.79</v>
@@ -9677,22 +9698,22 @@
         <v>31</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" s="4">
-        <v>220.16</v>
+        <v>222.98</v>
       </c>
       <c r="D27" s="4">
-        <v>226.29</v>
+        <v>234.62</v>
       </c>
       <c r="E27" s="4">
-        <v>203.4</v>
+        <v>210.89</v>
       </c>
       <c r="F27" s="4">
-        <v>226.29</v>
+        <v>234.62</v>
       </c>
       <c r="G27" s="4">
-        <v>6.35</v>
+        <v>10.26</v>
       </c>
       <c r="H27" s="4">
         <v>212.79</v>
@@ -9706,31 +9727,31 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" s="4">
-        <v>219.22</v>
+        <v>220.16</v>
       </c>
       <c r="D28" s="4">
-        <v>237.12</v>
+        <v>226.29</v>
       </c>
       <c r="E28" s="4">
-        <v>214.93</v>
+        <v>203.4</v>
       </c>
       <c r="F28" s="4">
-        <v>237.12</v>
+        <v>226.29</v>
       </c>
       <c r="G28" s="4">
-        <v>11.39</v>
+        <v>6.35</v>
       </c>
       <c r="H28" s="4">
-        <v>212.87</v>
-      </c>
-      <c r="I28" s="5">
-        <v>85</v>
+        <v>212.79</v>
+      </c>
+      <c r="I28" s="4">
+        <v>83.3</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>12</v>
@@ -9741,22 +9762,22 @@
         <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C29" s="4">
-        <v>216.66</v>
+        <v>219.22</v>
       </c>
       <c r="D29" s="4">
-        <v>226.93</v>
+        <v>237.12</v>
       </c>
       <c r="E29" s="4">
         <v>214.93</v>
       </c>
       <c r="F29" s="4">
-        <v>226.93</v>
+        <v>237.12</v>
       </c>
       <c r="G29" s="4">
-        <v>6.61</v>
+        <v>11.39</v>
       </c>
       <c r="H29" s="4">
         <v>212.87</v>
@@ -9773,22 +9794,22 @@
         <v>10</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C30" s="4">
-        <v>214.1</v>
+        <v>216.66</v>
       </c>
       <c r="D30" s="4">
-        <v>220.87</v>
+        <v>226.93</v>
       </c>
       <c r="E30" s="4">
-        <v>207.8</v>
+        <v>214.93</v>
       </c>
       <c r="F30" s="4">
-        <v>219.4</v>
+        <v>226.93</v>
       </c>
       <c r="G30" s="4">
-        <v>3.07</v>
+        <v>6.61</v>
       </c>
       <c r="H30" s="4">
         <v>212.87</v>
@@ -9802,28 +9823,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="3" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" s="4">
-        <v>219.11</v>
-      </c>
-      <c r="D31" s="5">
-        <v>237</v>
+        <v>214.1</v>
+      </c>
+      <c r="D31" s="4">
+        <v>220.87</v>
       </c>
       <c r="E31" s="4">
-        <v>214.85</v>
-      </c>
-      <c r="F31" s="5">
-        <v>237</v>
+        <v>207.8</v>
+      </c>
+      <c r="F31" s="4">
+        <v>219.4</v>
       </c>
       <c r="G31" s="4">
-        <v>11.35</v>
+        <v>3.07</v>
       </c>
       <c r="H31" s="4">
-        <v>212.84</v>
+        <v>212.87</v>
       </c>
       <c r="I31" s="5">
         <v>85</v>
@@ -9837,22 +9858,22 @@
         <v>32</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C32" s="4">
-        <v>216.55</v>
-      </c>
-      <c r="D32" s="4">
-        <v>226.82</v>
+        <v>219.11</v>
+      </c>
+      <c r="D32" s="5">
+        <v>237</v>
       </c>
       <c r="E32" s="4">
         <v>214.85</v>
       </c>
-      <c r="F32" s="4">
-        <v>226.82</v>
+      <c r="F32" s="5">
+        <v>237</v>
       </c>
       <c r="G32" s="4">
-        <v>6.57</v>
+        <v>11.35</v>
       </c>
       <c r="H32" s="4">
         <v>212.84</v>
@@ -9869,22 +9890,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" s="4">
-        <v>213.98</v>
+        <v>216.55</v>
       </c>
       <c r="D33" s="4">
-        <v>220.87</v>
+        <v>226.82</v>
       </c>
       <c r="E33" s="4">
-        <v>207.72</v>
+        <v>214.85</v>
       </c>
       <c r="F33" s="4">
-        <v>219.29</v>
+        <v>226.82</v>
       </c>
       <c r="G33" s="4">
-        <v>3.03</v>
+        <v>6.57</v>
       </c>
       <c r="H33" s="4">
         <v>212.84</v>
@@ -9898,28 +9919,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C34" s="4">
-        <v>219.17</v>
+        <v>213.98</v>
       </c>
       <c r="D34" s="4">
-        <v>236.94</v>
+        <v>220.87</v>
       </c>
       <c r="E34" s="4">
-        <v>214.73</v>
+        <v>207.72</v>
       </c>
       <c r="F34" s="4">
-        <v>236.94</v>
+        <v>219.29</v>
       </c>
       <c r="G34" s="4">
-        <v>11.38</v>
+        <v>3.03</v>
       </c>
       <c r="H34" s="4">
-        <v>212.73</v>
+        <v>212.84</v>
       </c>
       <c r="I34" s="5">
         <v>85</v>
@@ -9933,22 +9954,22 @@
         <v>16</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C35" s="4">
-        <v>216.6</v>
+        <v>219.17</v>
       </c>
       <c r="D35" s="4">
-        <v>226.76</v>
+        <v>236.94</v>
       </c>
       <c r="E35" s="4">
         <v>214.73</v>
       </c>
       <c r="F35" s="4">
-        <v>226.76</v>
+        <v>236.94</v>
       </c>
       <c r="G35" s="4">
-        <v>6.59</v>
+        <v>11.38</v>
       </c>
       <c r="H35" s="4">
         <v>212.73</v>
@@ -9965,22 +9986,22 @@
         <v>16</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="4">
-        <v>214.04</v>
+        <v>216.6</v>
       </c>
       <c r="D36" s="4">
-        <v>220.93</v>
+        <v>226.76</v>
       </c>
       <c r="E36" s="4">
-        <v>207.6</v>
+        <v>214.73</v>
       </c>
       <c r="F36" s="4">
-        <v>219.23</v>
+        <v>226.76</v>
       </c>
       <c r="G36" s="4">
-        <v>3.05</v>
+        <v>6.59</v>
       </c>
       <c r="H36" s="4">
         <v>212.73</v>
@@ -9994,28 +10015,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C37" s="4">
-        <v>220.51</v>
+        <v>214.04</v>
       </c>
       <c r="D37" s="4">
-        <v>236.57</v>
+        <v>220.93</v>
       </c>
       <c r="E37" s="4">
-        <v>215.8</v>
+        <v>207.6</v>
       </c>
       <c r="F37" s="4">
-        <v>236.57</v>
+        <v>219.23</v>
       </c>
       <c r="G37" s="4">
-        <v>10.67</v>
+        <v>3.05</v>
       </c>
       <c r="H37" s="4">
-        <v>213.77</v>
+        <v>212.73</v>
       </c>
       <c r="I37" s="5">
         <v>85</v>
@@ -10029,22 +10050,22 @@
         <v>17</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C38" s="4">
-        <v>217.95</v>
+        <v>220.51</v>
       </c>
       <c r="D38" s="4">
-        <v>226.46</v>
+        <v>236.57</v>
       </c>
       <c r="E38" s="4">
         <v>215.8</v>
       </c>
       <c r="F38" s="4">
-        <v>226.46</v>
+        <v>236.57</v>
       </c>
       <c r="G38" s="4">
-        <v>5.94</v>
+        <v>10.67</v>
       </c>
       <c r="H38" s="4">
         <v>213.77</v>
@@ -10061,22 +10082,22 @@
         <v>17</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39" s="4">
-        <v>215.39</v>
+        <v>217.95</v>
       </c>
       <c r="D39" s="4">
-        <v>220.62</v>
+        <v>226.46</v>
       </c>
       <c r="E39" s="4">
-        <v>208.68</v>
+        <v>215.8</v>
       </c>
       <c r="F39" s="4">
-        <v>218.99</v>
+        <v>226.46</v>
       </c>
       <c r="G39" s="4">
-        <v>2.44</v>
+        <v>5.94</v>
       </c>
       <c r="H39" s="4">
         <v>213.77</v>
@@ -10090,25 +10111,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C40" s="4">
-        <v>220.49</v>
+        <v>215.39</v>
       </c>
       <c r="D40" s="4">
-        <v>236.46</v>
+        <v>220.62</v>
       </c>
       <c r="E40" s="4">
-        <v>215.97</v>
+        <v>208.68</v>
       </c>
       <c r="F40" s="4">
-        <v>236.46</v>
+        <v>218.99</v>
       </c>
       <c r="G40" s="4">
-        <v>10.62</v>
+        <v>2.44</v>
       </c>
       <c r="H40" s="4">
         <v>213.77</v>
@@ -10125,22 +10146,22 @@
         <v>18</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C41" s="4">
-        <v>217.93</v>
+        <v>220.49</v>
       </c>
       <c r="D41" s="4">
-        <v>226.36</v>
+        <v>236.46</v>
       </c>
       <c r="E41" s="4">
         <v>215.97</v>
       </c>
       <c r="F41" s="4">
-        <v>226.36</v>
+        <v>236.46</v>
       </c>
       <c r="G41" s="4">
-        <v>5.89</v>
+        <v>10.62</v>
       </c>
       <c r="H41" s="4">
         <v>213.77</v>
@@ -10157,22 +10178,22 @@
         <v>18</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C42" s="4">
-        <v>215.37</v>
+        <v>217.93</v>
       </c>
       <c r="D42" s="4">
-        <v>220.77</v>
+        <v>226.36</v>
       </c>
       <c r="E42" s="4">
-        <v>208.85</v>
+        <v>215.97</v>
       </c>
       <c r="F42" s="4">
-        <v>218.89</v>
+        <v>226.36</v>
       </c>
       <c r="G42" s="4">
-        <v>2.4</v>
+        <v>5.89</v>
       </c>
       <c r="H42" s="4">
         <v>213.77</v>
@@ -10186,25 +10207,25 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C43" s="4">
-        <v>220.52</v>
+        <v>215.37</v>
       </c>
       <c r="D43" s="4">
-        <v>236.42</v>
+        <v>220.77</v>
       </c>
       <c r="E43" s="4">
-        <v>215.98</v>
+        <v>208.85</v>
       </c>
       <c r="F43" s="4">
-        <v>236.42</v>
+        <v>218.89</v>
       </c>
       <c r="G43" s="4">
-        <v>10.6</v>
+        <v>2.4</v>
       </c>
       <c r="H43" s="4">
         <v>213.77</v>
@@ -10221,22 +10242,22 @@
         <v>19</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C44" s="4">
-        <v>217.96</v>
+        <v>220.52</v>
       </c>
       <c r="D44" s="4">
-        <v>226.32</v>
+        <v>236.42</v>
       </c>
       <c r="E44" s="4">
         <v>215.98</v>
       </c>
       <c r="F44" s="4">
-        <v>226.32</v>
+        <v>236.42</v>
       </c>
       <c r="G44" s="4">
-        <v>5.87</v>
+        <v>10.6</v>
       </c>
       <c r="H44" s="4">
         <v>213.77</v>
@@ -10253,22 +10274,22 @@
         <v>19</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C45" s="4">
-        <v>215.39</v>
+        <v>217.96</v>
       </c>
       <c r="D45" s="4">
-        <v>220.93</v>
+        <v>226.32</v>
       </c>
       <c r="E45" s="4">
-        <v>208.86</v>
+        <v>215.98</v>
       </c>
       <c r="F45" s="4">
-        <v>218.85</v>
+        <v>226.32</v>
       </c>
       <c r="G45" s="4">
-        <v>2.38</v>
+        <v>5.87</v>
       </c>
       <c r="H45" s="4">
         <v>213.77</v>
@@ -10282,34 +10303,34 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C46" s="4">
-        <v>231.28</v>
+        <v>215.39</v>
       </c>
       <c r="D46" s="4">
-        <v>233.5</v>
+        <v>220.93</v>
       </c>
       <c r="E46" s="4">
-        <v>213.06</v>
+        <v>208.86</v>
       </c>
       <c r="F46" s="4">
-        <v>233.5</v>
+        <v>218.85</v>
       </c>
       <c r="G46" s="4">
-        <v>-2.28</v>
+        <v>2.38</v>
       </c>
       <c r="H46" s="4">
-        <v>238.95</v>
-      </c>
-      <c r="I46" s="4">
-        <v>83.3</v>
+        <v>213.77</v>
+      </c>
+      <c r="I46" s="5">
+        <v>85</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
@@ -10317,22 +10338,22 @@
         <v>33</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C47" s="4">
-        <v>229.07</v>
+        <v>231.28</v>
       </c>
       <c r="D47" s="4">
-        <v>229.07</v>
+        <v>233.5</v>
       </c>
       <c r="E47" s="4">
         <v>213.06</v>
       </c>
       <c r="F47" s="4">
-        <v>225.27</v>
+        <v>233.5</v>
       </c>
       <c r="G47" s="4">
-        <v>-5.72</v>
+        <v>-2.28</v>
       </c>
       <c r="H47" s="4">
         <v>238.95</v>
@@ -10349,22 +10370,22 @@
         <v>33</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C48" s="4">
-        <v>226.87</v>
+        <v>229.07</v>
       </c>
       <c r="D48" s="4">
-        <v>226.87</v>
+        <v>229.07</v>
       </c>
       <c r="E48" s="4">
-        <v>207.31</v>
+        <v>213.06</v>
       </c>
       <c r="F48" s="4">
-        <v>219.19</v>
+        <v>225.27</v>
       </c>
       <c r="G48" s="4">
-        <v>-8.27</v>
+        <v>-5.72</v>
       </c>
       <c r="H48" s="4">
         <v>238.95</v>
@@ -10378,28 +10399,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C49" s="4">
-        <v>231.35</v>
+        <v>226.87</v>
       </c>
       <c r="D49" s="4">
-        <v>233.54</v>
+        <v>226.87</v>
       </c>
       <c r="E49" s="4">
-        <v>213.32</v>
+        <v>207.31</v>
       </c>
       <c r="F49" s="4">
-        <v>233.54</v>
+        <v>219.19</v>
       </c>
       <c r="G49" s="4">
-        <v>-2.31</v>
+        <v>-8.27</v>
       </c>
       <c r="H49" s="4">
-        <v>239.06</v>
+        <v>238.95</v>
       </c>
       <c r="I49" s="4">
         <v>83.3</v>
@@ -10413,22 +10434,22 @@
         <v>35</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C50" s="4">
-        <v>229.14</v>
+        <v>231.35</v>
       </c>
       <c r="D50" s="4">
-        <v>229.14</v>
+        <v>233.54</v>
       </c>
       <c r="E50" s="4">
         <v>213.32</v>
       </c>
       <c r="F50" s="4">
-        <v>225.32</v>
+        <v>233.54</v>
       </c>
       <c r="G50" s="4">
-        <v>-5.75</v>
+        <v>-2.31</v>
       </c>
       <c r="H50" s="4">
         <v>239.06</v>
@@ -10445,22 +10466,22 @@
         <v>35</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C51" s="4">
-        <v>226.94</v>
+        <v>229.14</v>
       </c>
       <c r="D51" s="4">
-        <v>226.94</v>
+        <v>229.14</v>
       </c>
       <c r="E51" s="4">
-        <v>207.57</v>
+        <v>213.32</v>
       </c>
       <c r="F51" s="4">
-        <v>219.25</v>
+        <v>225.32</v>
       </c>
       <c r="G51" s="4">
-        <v>-8.29</v>
+        <v>-5.75</v>
       </c>
       <c r="H51" s="4">
         <v>239.06</v>
@@ -10469,6 +10490,38 @@
         <v>83.3</v>
       </c>
       <c r="J51" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
+      <c r="A52" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="4">
+        <v>226.94</v>
+      </c>
+      <c r="D52" s="4">
+        <v>226.94</v>
+      </c>
+      <c r="E52" s="4">
+        <v>207.57</v>
+      </c>
+      <c r="F52" s="4">
+        <v>219.25</v>
+      </c>
+      <c r="G52" s="4">
+        <v>-8.29</v>
+      </c>
+      <c r="H52" s="4">
+        <v>239.06</v>
+      </c>
+      <c r="I52" s="4">
+        <v>83.3</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>34</v>
       </c>
     </row>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPY" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,25 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -52,49 +41,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -105,46 +57,16 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -223,10 +145,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -264,71 +186,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -352,53 +272,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -408,7 +329,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -417,7 +338,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -426,7 +347,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -434,10 +355,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -466,7 +387,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -479,12 +400,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -507,56 +429,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exported At</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Profit %</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
@@ -3871,168 +3793,218 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-07 20:09</t>
+          <t>2026-04-16 13:40:34</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Pred 646.3  →  Actual 676.01</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>718.86</v>
+      </c>
+      <c r="D89" t="n">
+        <v>718.86</v>
+      </c>
+      <c r="E89" t="n">
+        <v>677.25</v>
+      </c>
+      <c r="F89" t="n">
+        <v>682.86</v>
       </c>
       <c r="G89" t="n">
-        <v>4.6</v>
+        <v>-2.44</v>
       </c>
       <c r="H89" t="n">
-        <v>676.01</v>
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I89" t="n">
+        <v>83.3</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-07 20:42</t>
+          <t>2026-04-16 13:40:34</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Pred 646.07  →  Actual 676.01</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>715.5700000000001</v>
+      </c>
+      <c r="D90" t="n">
+        <v>715.5700000000001</v>
+      </c>
+      <c r="E90" t="n">
+        <v>671.13</v>
+      </c>
+      <c r="F90" t="n">
+        <v>671.13</v>
       </c>
       <c r="G90" t="n">
-        <v>4.63</v>
+        <v>-4.12</v>
       </c>
       <c r="H90" t="n">
-        <v>676.01</v>
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I90" t="n">
+        <v>83.3</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-08 23:29</t>
+          <t>2026-04-16 13:40:34</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Pred 663.51  →  Actual 679.91</t>
-        </is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>712.27</v>
+      </c>
+      <c r="D91" t="n">
+        <v>712.27</v>
+      </c>
+      <c r="E91" t="n">
+        <v>662.46</v>
+      </c>
+      <c r="F91" t="n">
+        <v>662.46</v>
       </c>
       <c r="G91" t="n">
-        <v>2.47</v>
+        <v>-5.35</v>
       </c>
       <c r="H91" t="n">
-        <v>679.91</v>
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I91" t="n">
+        <v>83.3</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>✓ In range</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-04-13 00:26</t>
+          <t>2026-04-16 13:48:18</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Pred 649.66  →  Actual 694.46</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>718.79</v>
+      </c>
+      <c r="D92" t="n">
+        <v>718.79</v>
+      </c>
+      <c r="E92" t="n">
+        <v>677.48</v>
+      </c>
+      <c r="F92" t="n">
+        <v>682.34</v>
       </c>
       <c r="G92" t="n">
-        <v>6.9</v>
+        <v>-2.52</v>
       </c>
       <c r="H92" t="n">
-        <v>694.46</v>
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I92" t="n">
+        <v>83.3</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-04-14 02:44</t>
+          <t>2026-04-16 13:48:18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Pred 655.38  →  Actual 699.94</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>715.49</v>
+      </c>
+      <c r="D93" t="n">
+        <v>715.49</v>
+      </c>
+      <c r="E93" t="n">
+        <v>670.62</v>
+      </c>
+      <c r="F93" t="n">
+        <v>670.62</v>
       </c>
       <c r="G93" t="n">
-        <v>6.8</v>
+        <v>-4.19</v>
       </c>
       <c r="H93" t="n">
         <v>699.9400000000001</v>
       </c>
+      <c r="I93" t="n">
+        <v>83.3</v>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:34</t>
+          <t>2026-04-16 13:48:18</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Best Case</t>
+          <t>Worst Case</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>718.86</v>
+        <v>712.2</v>
       </c>
       <c r="D94" t="n">
-        <v>718.86</v>
+        <v>712.2</v>
       </c>
       <c r="E94" t="n">
-        <v>677.25</v>
+        <v>661.96</v>
       </c>
       <c r="F94" t="n">
-        <v>682.86</v>
+        <v>661.96</v>
       </c>
       <c r="G94" t="n">
-        <v>-2.44</v>
+        <v>-5.43</v>
       </c>
       <c r="H94" t="n">
         <v>699.9400000000001</v>
@@ -4041,336 +4013,6 @@
         <v>83.3</v>
       </c>
       <c r="J94" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:34</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>715.5700000000001</v>
-      </c>
-      <c r="D95" t="n">
-        <v>715.5700000000001</v>
-      </c>
-      <c r="E95" t="n">
-        <v>671.13</v>
-      </c>
-      <c r="F95" t="n">
-        <v>671.13</v>
-      </c>
-      <c r="G95" t="n">
-        <v>-4.12</v>
-      </c>
-      <c r="H95" t="n">
-        <v>699.9400000000001</v>
-      </c>
-      <c r="I95" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:34</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>712.27</v>
-      </c>
-      <c r="D96" t="n">
-        <v>712.27</v>
-      </c>
-      <c r="E96" t="n">
-        <v>662.46</v>
-      </c>
-      <c r="F96" t="n">
-        <v>662.46</v>
-      </c>
-      <c r="G96" t="n">
-        <v>-5.35</v>
-      </c>
-      <c r="H96" t="n">
-        <v>699.9400000000001</v>
-      </c>
-      <c r="I96" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-04-07 20:09</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Pred 646.3  →  Actual 676.01</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H97" t="n">
-        <v>676.01</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-04-07 20:42</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Pred 646.07  →  Actual 676.01</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="H98" t="n">
-        <v>676.01</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-04-08 23:29</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Pred 663.51  →  Actual 679.91</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="H99" t="n">
-        <v>679.91</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>✓ In range</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-04-13 00:26</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Pred 649.66  →  Actual 694.46</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H100" t="n">
-        <v>694.46</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:44</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Pred 655.38  →  Actual 699.94</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H101" t="n">
-        <v>699.9400000000001</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:18</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>718.79</v>
-      </c>
-      <c r="D102" t="n">
-        <v>718.79</v>
-      </c>
-      <c r="E102" t="n">
-        <v>677.48</v>
-      </c>
-      <c r="F102" t="n">
-        <v>682.34</v>
-      </c>
-      <c r="G102" t="n">
-        <v>-2.52</v>
-      </c>
-      <c r="H102" t="n">
-        <v>699.9400000000001</v>
-      </c>
-      <c r="I102" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:18</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>715.49</v>
-      </c>
-      <c r="D103" t="n">
-        <v>715.49</v>
-      </c>
-      <c r="E103" t="n">
-        <v>670.62</v>
-      </c>
-      <c r="F103" t="n">
-        <v>670.62</v>
-      </c>
-      <c r="G103" t="n">
-        <v>-4.19</v>
-      </c>
-      <c r="H103" t="n">
-        <v>699.9400000000001</v>
-      </c>
-      <c r="I103" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:18</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>712.2</v>
-      </c>
-      <c r="D104" t="n">
-        <v>712.2</v>
-      </c>
-      <c r="E104" t="n">
-        <v>661.96</v>
-      </c>
-      <c r="F104" t="n">
-        <v>661.96</v>
-      </c>
-      <c r="G104" t="n">
-        <v>-5.43</v>
-      </c>
-      <c r="H104" t="n">
-        <v>699.9400000000001</v>
-      </c>
-      <c r="I104" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J104" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4387,56 +4029,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exported At</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Profit %</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
@@ -7751,168 +7393,218 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-07 20:10</t>
+          <t>2026-04-16 13:40:34</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Pred 262.15  →  Actual 258.9</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>286</v>
+      </c>
+      <c r="D89" t="n">
+        <v>286</v>
+      </c>
+      <c r="E89" t="n">
+        <v>266.96</v>
+      </c>
+      <c r="F89" t="n">
+        <v>275.93</v>
       </c>
       <c r="G89" t="n">
-        <v>-1.24</v>
+        <v>3.56</v>
       </c>
       <c r="H89" t="n">
-        <v>258.9</v>
+        <v>266.43</v>
+      </c>
+      <c r="I89" t="n">
+        <v>83.3</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>✓ In range</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-07 20:42</t>
+          <t>2026-04-16 13:40:34</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Pred 262.64  →  Actual 258.9</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="D90" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="E90" t="n">
+        <v>266.96</v>
+      </c>
+      <c r="F90" t="n">
+        <v>268.71</v>
       </c>
       <c r="G90" t="n">
-        <v>-1.42</v>
+        <v>0.85</v>
       </c>
       <c r="H90" t="n">
-        <v>258.9</v>
+        <v>266.43</v>
+      </c>
+      <c r="I90" t="n">
+        <v>83.3</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>✓ In range</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-08 23:30</t>
+          <t>2026-04-16 13:40:34</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Pred 269.21  →  Actual 260.49</t>
-        </is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>281.98</v>
+      </c>
+      <c r="D91" t="n">
+        <v>281.98</v>
+      </c>
+      <c r="E91" t="n">
+        <v>261.66</v>
+      </c>
+      <c r="F91" t="n">
+        <v>263.37</v>
       </c>
       <c r="G91" t="n">
-        <v>-3.24</v>
+        <v>-1.15</v>
       </c>
       <c r="H91" t="n">
-        <v>260.49</v>
+        <v>266.43</v>
+      </c>
+      <c r="I91" t="n">
+        <v>83.3</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-04-13 00:25</t>
+          <t>2026-04-16 13:48:18</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Pred 268.65  →  Actual 258.83</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>286.29</v>
+      </c>
+      <c r="D92" t="n">
+        <v>286.29</v>
+      </c>
+      <c r="E92" t="n">
+        <v>267.06</v>
+      </c>
+      <c r="F92" t="n">
+        <v>275.65</v>
       </c>
       <c r="G92" t="n">
-        <v>-3.66</v>
+        <v>3.46</v>
       </c>
       <c r="H92" t="n">
-        <v>258.83</v>
+        <v>266.43</v>
+      </c>
+      <c r="I92" t="n">
+        <v>83.3</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-04-14 02:44</t>
+          <t>2026-04-16 13:48:18</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Pred 267.8  →  Actual 266.43</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>284.27</v>
+      </c>
+      <c r="D93" t="n">
+        <v>284.27</v>
+      </c>
+      <c r="E93" t="n">
+        <v>267.06</v>
+      </c>
+      <c r="F93" t="n">
+        <v>268.44</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.51</v>
+        <v>0.75</v>
       </c>
       <c r="H93" t="n">
         <v>266.43</v>
       </c>
+      <c r="I93" t="n">
+        <v>83.3</v>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>✓ In range</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:34</t>
+          <t>2026-04-16 13:48:18</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Best Case</t>
+          <t>Worst Case</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>286</v>
+        <v>282.26</v>
       </c>
       <c r="D94" t="n">
-        <v>286</v>
+        <v>282.26</v>
       </c>
       <c r="E94" t="n">
-        <v>266.96</v>
+        <v>261.75</v>
       </c>
       <c r="F94" t="n">
-        <v>275.93</v>
+        <v>263.1</v>
       </c>
       <c r="G94" t="n">
-        <v>3.56</v>
+        <v>-1.25</v>
       </c>
       <c r="H94" t="n">
         <v>266.43</v>
@@ -7921,336 +7613,6 @@
         <v>83.3</v>
       </c>
       <c r="J94" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:34</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="D95" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="E95" t="n">
-        <v>266.96</v>
-      </c>
-      <c r="F95" t="n">
-        <v>268.71</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H95" t="n">
-        <v>266.43</v>
-      </c>
-      <c r="I95" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:34</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>281.98</v>
-      </c>
-      <c r="D96" t="n">
-        <v>281.98</v>
-      </c>
-      <c r="E96" t="n">
-        <v>261.66</v>
-      </c>
-      <c r="F96" t="n">
-        <v>263.37</v>
-      </c>
-      <c r="G96" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="H96" t="n">
-        <v>266.43</v>
-      </c>
-      <c r="I96" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-04-07 20:10</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Pred 262.15  →  Actual 258.9</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="H97" t="n">
-        <v>258.9</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>✓ In range</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-04-07 20:42</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Pred 262.64  →  Actual 258.9</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="H98" t="n">
-        <v>258.9</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>✓ In range</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-04-08 23:30</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Pred 269.21  →  Actual 260.49</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>-3.24</v>
-      </c>
-      <c r="H99" t="n">
-        <v>260.49</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-04-13 00:25</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Pred 268.65  →  Actual 258.83</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="H100" t="n">
-        <v>258.83</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:44</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Pred 267.8  →  Actual 266.43</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="H101" t="n">
-        <v>266.43</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>✓ In range</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:18</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>286.29</v>
-      </c>
-      <c r="D102" t="n">
-        <v>286.29</v>
-      </c>
-      <c r="E102" t="n">
-        <v>267.06</v>
-      </c>
-      <c r="F102" t="n">
-        <v>275.65</v>
-      </c>
-      <c r="G102" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="H102" t="n">
-        <v>266.43</v>
-      </c>
-      <c r="I102" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:18</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>284.27</v>
-      </c>
-      <c r="D103" t="n">
-        <v>284.27</v>
-      </c>
-      <c r="E103" t="n">
-        <v>267.06</v>
-      </c>
-      <c r="F103" t="n">
-        <v>268.44</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H103" t="n">
-        <v>266.43</v>
-      </c>
-      <c r="I103" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:18</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>282.26</v>
-      </c>
-      <c r="D104" t="n">
-        <v>282.26</v>
-      </c>
-      <c r="E104" t="n">
-        <v>261.75</v>
-      </c>
-      <c r="F104" t="n">
-        <v>263.1</v>
-      </c>
-      <c r="G104" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="H104" t="n">
-        <v>266.43</v>
-      </c>
-      <c r="I104" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J104" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -8267,56 +7629,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exported At</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Profit %</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
@@ -11631,506 +10993,226 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-07 20:09</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Pred 338.56  →  Actual 374.33</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>387.53</v>
+      </c>
+      <c r="D89" t="n">
+        <v>476.45</v>
+      </c>
+      <c r="E89" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>453.03</v>
       </c>
       <c r="G89" t="n">
-        <v>10.57</v>
+        <v>10.17</v>
       </c>
       <c r="H89" t="n">
-        <v>374.33</v>
+        <v>411.22</v>
+      </c>
+      <c r="I89" t="n">
+        <v>83.3</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-07 20:42</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Pred 337.75  →  Actual 374.33</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>384.87</v>
+      </c>
+      <c r="D90" t="n">
+        <v>464.28</v>
+      </c>
+      <c r="E90" t="n">
+        <v>381.1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>441.46</v>
       </c>
       <c r="G90" t="n">
-        <v>10.83</v>
+        <v>7.35</v>
       </c>
       <c r="H90" t="n">
-        <v>374.33</v>
+        <v>411.22</v>
+      </c>
+      <c r="I90" t="n">
+        <v>83.3</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-08 23:29</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Pred 398.27  →  Actual 373.07</t>
-        </is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>382.21</v>
+      </c>
+      <c r="D91" t="n">
+        <v>464.28</v>
+      </c>
+      <c r="E91" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="F91" t="n">
+        <v>432.9</v>
       </c>
       <c r="G91" t="n">
-        <v>-6.33</v>
+        <v>5.27</v>
       </c>
       <c r="H91" t="n">
-        <v>373.07</v>
+        <v>411.22</v>
+      </c>
+      <c r="I91" t="n">
+        <v>83.3</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-04-13 00:26</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Pred 376.61  →  Actual 393.11</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>383.74</v>
+      </c>
+      <c r="D92" t="n">
+        <v>477.95</v>
+      </c>
+      <c r="E92" t="n">
+        <v>379.61</v>
+      </c>
+      <c r="F92" t="n">
+        <v>446.33</v>
       </c>
       <c r="G92" t="n">
-        <v>4.38</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>393.11</v>
+        <v>411.22</v>
+      </c>
+      <c r="I92" t="n">
+        <v>81.7</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-04-14 02:44</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Pred 361.76  →  Actual 411.22</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>381.11</v>
+      </c>
+      <c r="D93" t="n">
+        <v>465.74</v>
+      </c>
+      <c r="E93" t="n">
+        <v>379.61</v>
+      </c>
+      <c r="F93" t="n">
+        <v>434.92</v>
       </c>
       <c r="G93" t="n">
-        <v>13.67</v>
+        <v>5.76</v>
       </c>
       <c r="H93" t="n">
         <v>411.22</v>
       </c>
+      <c r="I93" t="n">
+        <v>81.7</v>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:35</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Best Case</t>
+          <t>Worst Case</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>387.53</v>
+        <v>378.47</v>
       </c>
       <c r="D94" t="n">
-        <v>476.45</v>
+        <v>465.74</v>
       </c>
       <c r="E94" t="n">
-        <v>381.1</v>
+        <v>372.25</v>
       </c>
       <c r="F94" t="n">
-        <v>453.03</v>
+        <v>426.5</v>
       </c>
       <c r="G94" t="n">
-        <v>10.17</v>
+        <v>3.71</v>
       </c>
       <c r="H94" t="n">
         <v>411.22</v>
       </c>
       <c r="I94" t="n">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="J94" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:35</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>384.87</v>
-      </c>
-      <c r="D95" t="n">
-        <v>464.28</v>
-      </c>
-      <c r="E95" t="n">
-        <v>381.1</v>
-      </c>
-      <c r="F95" t="n">
-        <v>441.46</v>
-      </c>
-      <c r="G95" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="H95" t="n">
-        <v>411.22</v>
-      </c>
-      <c r="I95" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:35</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>382.21</v>
-      </c>
-      <c r="D96" t="n">
-        <v>464.28</v>
-      </c>
-      <c r="E96" t="n">
-        <v>373.71</v>
-      </c>
-      <c r="F96" t="n">
-        <v>432.9</v>
-      </c>
-      <c r="G96" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="H96" t="n">
-        <v>411.22</v>
-      </c>
-      <c r="I96" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-04-07 20:09</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Pred 338.56  →  Actual 374.33</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="H97" t="n">
-        <v>374.33</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-04-07 20:42</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Pred 337.75  →  Actual 374.33</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="H98" t="n">
-        <v>374.33</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-04-08 23:29</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Pred 398.27  →  Actual 373.07</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>-6.33</v>
-      </c>
-      <c r="H99" t="n">
-        <v>373.07</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-04-13 00:26</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Pred 376.61  →  Actual 393.11</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="H100" t="n">
-        <v>393.11</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:44</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Pred 361.76  →  Actual 411.22</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="H101" t="n">
-        <v>411.22</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>383.74</v>
-      </c>
-      <c r="D102" t="n">
-        <v>477.95</v>
-      </c>
-      <c r="E102" t="n">
-        <v>379.61</v>
-      </c>
-      <c r="F102" t="n">
-        <v>446.33</v>
-      </c>
-      <c r="G102" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="H102" t="n">
-        <v>411.22</v>
-      </c>
-      <c r="I102" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>381.11</v>
-      </c>
-      <c r="D103" t="n">
-        <v>465.74</v>
-      </c>
-      <c r="E103" t="n">
-        <v>379.61</v>
-      </c>
-      <c r="F103" t="n">
-        <v>434.92</v>
-      </c>
-      <c r="G103" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="H103" t="n">
-        <v>411.22</v>
-      </c>
-      <c r="I103" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>378.47</v>
-      </c>
-      <c r="D104" t="n">
-        <v>465.74</v>
-      </c>
-      <c r="E104" t="n">
-        <v>372.25</v>
-      </c>
-      <c r="F104" t="n">
-        <v>426.5</v>
-      </c>
-      <c r="G104" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="H104" t="n">
-        <v>411.22</v>
-      </c>
-      <c r="I104" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="J104" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -12147,56 +11229,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exported At</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Profit %</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
@@ -14257,168 +13339,218 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-07 20:09</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Pred 234.71  →  Actual 221.25</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>235.06</v>
+      </c>
+      <c r="D56" t="n">
+        <v>240.15</v>
+      </c>
+      <c r="E56" t="n">
+        <v>210.37</v>
+      </c>
+      <c r="F56" t="n">
+        <v>240.15</v>
       </c>
       <c r="G56" t="n">
-        <v>-5.74</v>
+        <v>-3.36</v>
       </c>
       <c r="H56" t="n">
-        <v>221.25</v>
+        <v>248.5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>81.7</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-07 20:42</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Pred 234.55  →  Actual 221.25</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>232.54</v>
+      </c>
+      <c r="D57" t="n">
+        <v>232.54</v>
+      </c>
+      <c r="E57" t="n">
+        <v>210.37</v>
+      </c>
+      <c r="F57" t="n">
+        <v>230.67</v>
       </c>
       <c r="G57" t="n">
-        <v>-5.67</v>
+        <v>-7.18</v>
       </c>
       <c r="H57" t="n">
-        <v>221.25</v>
+        <v>248.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>81.7</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-08 23:29</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Pred 224.42  →  Actual 233.65</t>
-        </is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>230.02</v>
+      </c>
+      <c r="D58" t="n">
+        <v>230.02</v>
+      </c>
+      <c r="E58" t="n">
+        <v>203.98</v>
+      </c>
+      <c r="F58" t="n">
+        <v>223.67</v>
       </c>
       <c r="G58" t="n">
-        <v>4.12</v>
+        <v>-9.99</v>
       </c>
       <c r="H58" t="n">
-        <v>233.65</v>
+        <v>248.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>81.7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-13 00:26</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Pred 211.33  →  Actual 249.02</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>234.63</v>
+      </c>
+      <c r="D59" t="n">
+        <v>239.91</v>
+      </c>
+      <c r="E59" t="n">
+        <v>210.37</v>
+      </c>
+      <c r="F59" t="n">
+        <v>239.91</v>
       </c>
       <c r="G59" t="n">
-        <v>17.83</v>
+        <v>-3.46</v>
       </c>
       <c r="H59" t="n">
-        <v>249.02</v>
+        <v>248.5</v>
+      </c>
+      <c r="I59" t="n">
+        <v>81.7</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-14 02:44</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Pred 225.39  →  Actual 248.5</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>232.12</v>
+      </c>
+      <c r="D60" t="n">
+        <v>232.12</v>
+      </c>
+      <c r="E60" t="n">
+        <v>210.37</v>
+      </c>
+      <c r="F60" t="n">
+        <v>230.44</v>
       </c>
       <c r="G60" t="n">
-        <v>10.25</v>
+        <v>-7.27</v>
       </c>
       <c r="H60" t="n">
         <v>248.5</v>
       </c>
+      <c r="I60" t="n">
+        <v>81.7</v>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:35</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Best Case</t>
+          <t>Worst Case</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>235.06</v>
+        <v>229.6</v>
       </c>
       <c r="D61" t="n">
-        <v>240.15</v>
+        <v>229.6</v>
       </c>
       <c r="E61" t="n">
-        <v>210.37</v>
+        <v>203.98</v>
       </c>
       <c r="F61" t="n">
-        <v>240.15</v>
+        <v>223.45</v>
       </c>
       <c r="G61" t="n">
-        <v>-3.36</v>
+        <v>-10.08</v>
       </c>
       <c r="H61" t="n">
         <v>248.5</v>
@@ -14427,336 +13559,6 @@
         <v>81.7</v>
       </c>
       <c r="J61" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:35</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>232.54</v>
-      </c>
-      <c r="D62" t="n">
-        <v>232.54</v>
-      </c>
-      <c r="E62" t="n">
-        <v>210.37</v>
-      </c>
-      <c r="F62" t="n">
-        <v>230.67</v>
-      </c>
-      <c r="G62" t="n">
-        <v>-7.18</v>
-      </c>
-      <c r="H62" t="n">
-        <v>248.5</v>
-      </c>
-      <c r="I62" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:40:35</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>230.02</v>
-      </c>
-      <c r="D63" t="n">
-        <v>230.02</v>
-      </c>
-      <c r="E63" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="F63" t="n">
-        <v>223.67</v>
-      </c>
-      <c r="G63" t="n">
-        <v>-9.99</v>
-      </c>
-      <c r="H63" t="n">
-        <v>248.5</v>
-      </c>
-      <c r="I63" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-04-07 20:09</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Pred 234.71  →  Actual 221.25</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>-5.74</v>
-      </c>
-      <c r="H64" t="n">
-        <v>221.25</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-04-07 20:42</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Pred 234.55  →  Actual 221.25</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>-5.67</v>
-      </c>
-      <c r="H65" t="n">
-        <v>221.25</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-04-08 23:29</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Pred 224.42  →  Actual 233.65</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="H66" t="n">
-        <v>233.65</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-04-13 00:26</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Pred 211.33  →  Actual 249.02</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>17.83</v>
-      </c>
-      <c r="H67" t="n">
-        <v>249.02</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:44</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Pred 225.39  →  Actual 248.5</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="H68" t="n">
-        <v>248.5</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>234.63</v>
-      </c>
-      <c r="D69" t="n">
-        <v>239.91</v>
-      </c>
-      <c r="E69" t="n">
-        <v>210.37</v>
-      </c>
-      <c r="F69" t="n">
-        <v>239.91</v>
-      </c>
-      <c r="G69" t="n">
-        <v>-3.46</v>
-      </c>
-      <c r="H69" t="n">
-        <v>248.5</v>
-      </c>
-      <c r="I69" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>232.12</v>
-      </c>
-      <c r="D70" t="n">
-        <v>232.12</v>
-      </c>
-      <c r="E70" t="n">
-        <v>210.37</v>
-      </c>
-      <c r="F70" t="n">
-        <v>230.44</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-7.27</v>
-      </c>
-      <c r="H70" t="n">
-        <v>248.5</v>
-      </c>
-      <c r="I70" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>229.6</v>
-      </c>
-      <c r="D71" t="n">
-        <v>229.6</v>
-      </c>
-      <c r="E71" t="n">
-        <v>203.98</v>
-      </c>
-      <c r="F71" t="n">
-        <v>223.45</v>
-      </c>
-      <c r="G71" t="n">
-        <v>-10.08</v>
-      </c>
-      <c r="H71" t="n">
-        <v>248.5</v>
-      </c>
-      <c r="I71" t="n">
-        <v>81.7</v>
-      </c>
-      <c r="J71" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -14773,56 +13575,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exported At</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Profit %</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
@@ -15857,103 +14659,121 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-08 23:29</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Pred 618.0  →  Actual 628.39</t>
-        </is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>533.34</v>
+      </c>
+      <c r="D29" t="n">
+        <v>701.64</v>
+      </c>
+      <c r="E29" t="n">
+        <v>533.34</v>
+      </c>
+      <c r="F29" t="n">
+        <v>701.64</v>
       </c>
       <c r="G29" t="n">
-        <v>1.68</v>
+        <v>4.48</v>
       </c>
       <c r="H29" t="n">
-        <v>628.39</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>671.58</v>
+      </c>
+      <c r="I29" t="n">
+        <v>83.3</v>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>✓ In range</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13 00:26</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Pred 693.48  →  Actual 662.49</t>
-        </is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>526.64</v>
+      </c>
+      <c r="D30" t="n">
+        <v>669.34</v>
+      </c>
+      <c r="E30" t="n">
+        <v>526.64</v>
+      </c>
+      <c r="F30" t="n">
+        <v>669.34</v>
       </c>
       <c r="G30" t="n">
-        <v>-4.47</v>
+        <v>-0.33</v>
       </c>
       <c r="H30" t="n">
-        <v>662.49</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>671.58</v>
+      </c>
+      <c r="I30" t="n">
+        <v>83.3</v>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-14 02:44</t>
+          <t>2026-04-16 13:40:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Pred 734.16  →  Actual 671.58</t>
-        </is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>519.9400000000001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>663.64</v>
+      </c>
+      <c r="E31" t="n">
+        <v>519.9400000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>645.47</v>
       </c>
       <c r="G31" t="n">
-        <v>-8.52</v>
+        <v>-3.89</v>
       </c>
       <c r="H31" t="n">
         <v>671.58</v>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>83.3</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>✗ Outside</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:35</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -15962,19 +14782,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>533.34</v>
+        <v>533.46</v>
       </c>
       <c r="D32" t="n">
-        <v>701.64</v>
+        <v>702.61</v>
       </c>
       <c r="E32" t="n">
-        <v>533.34</v>
+        <v>533.46</v>
       </c>
       <c r="F32" t="n">
-        <v>701.64</v>
+        <v>702.61</v>
       </c>
       <c r="G32" t="n">
-        <v>4.48</v>
+        <v>4.62</v>
       </c>
       <c r="H32" t="n">
         <v>671.58</v>
@@ -15991,7 +14811,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:35</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -16000,19 +14820,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>526.64</v>
+        <v>526.77</v>
       </c>
       <c r="D33" t="n">
-        <v>669.34</v>
+        <v>670.27</v>
       </c>
       <c r="E33" t="n">
-        <v>526.64</v>
+        <v>526.77</v>
       </c>
       <c r="F33" t="n">
-        <v>669.34</v>
+        <v>670.27</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.33</v>
+        <v>-0.19</v>
       </c>
       <c r="H33" t="n">
         <v>671.58</v>
@@ -16029,7 +14849,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-16 13:40:35</t>
+          <t>2026-04-16 13:48:19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -16038,19 +14858,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>519.9400000000001</v>
+        <v>520.0700000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>663.64</v>
+        <v>664.1900000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>519.9400000000001</v>
+        <v>520.0700000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>645.47</v>
+        <v>646.37</v>
       </c>
       <c r="G34" t="n">
-        <v>-3.89</v>
+        <v>-3.75</v>
       </c>
       <c r="H34" t="n">
         <v>671.58</v>
@@ -16059,216 +14879,6 @@
         <v>83.3</v>
       </c>
       <c r="J34" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-04-08 23:29</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Pred 618.0  →  Actual 628.39</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H35" t="n">
-        <v>628.39</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>✓ In range</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-04-13 00:26</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Pred 693.48  →  Actual 662.49</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>-4.47</v>
-      </c>
-      <c r="H36" t="n">
-        <v>662.49</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-04-14 02:44</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>── Daily Score ──</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Pred 734.16  →  Actual 671.58</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>-8.52</v>
-      </c>
-      <c r="H37" t="n">
-        <v>671.58</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>✗ Outside</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Best Case</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>533.46</v>
-      </c>
-      <c r="D38" t="n">
-        <v>702.61</v>
-      </c>
-      <c r="E38" t="n">
-        <v>533.46</v>
-      </c>
-      <c r="F38" t="n">
-        <v>702.61</v>
-      </c>
-      <c r="G38" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="H38" t="n">
-        <v>671.58</v>
-      </c>
-      <c r="I38" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Average Case</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>526.77</v>
-      </c>
-      <c r="D39" t="n">
-        <v>670.27</v>
-      </c>
-      <c r="E39" t="n">
-        <v>526.77</v>
-      </c>
-      <c r="F39" t="n">
-        <v>670.27</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="H39" t="n">
-        <v>671.58</v>
-      </c>
-      <c r="I39" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48:19</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Worst Case</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>520.0700000000001</v>
-      </c>
-      <c r="D40" t="n">
-        <v>664.1900000000001</v>
-      </c>
-      <c r="E40" t="n">
-        <v>520.0700000000001</v>
-      </c>
-      <c r="F40" t="n">
-        <v>646.37</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="H40" t="n">
-        <v>671.58</v>
-      </c>
-      <c r="I40" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="J40" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4013,6 +4013,234 @@
         <v>83.3</v>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>718.72</v>
+      </c>
+      <c r="D95" t="n">
+        <v>718.72</v>
+      </c>
+      <c r="E95" t="n">
+        <v>682.46</v>
+      </c>
+      <c r="F95" t="n">
+        <v>684.14</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-2.26</v>
+      </c>
+      <c r="H95" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I95" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>715.42</v>
+      </c>
+      <c r="D96" t="n">
+        <v>715.42</v>
+      </c>
+      <c r="E96" t="n">
+        <v>672.39</v>
+      </c>
+      <c r="F96" t="n">
+        <v>672.39</v>
+      </c>
+      <c r="G96" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="H96" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I96" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>712.13</v>
+      </c>
+      <c r="D97" t="n">
+        <v>712.13</v>
+      </c>
+      <c r="E97" t="n">
+        <v>663.71</v>
+      </c>
+      <c r="F97" t="n">
+        <v>663.71</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="H97" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I97" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>718.34</v>
+      </c>
+      <c r="D98" t="n">
+        <v>718.34</v>
+      </c>
+      <c r="E98" t="n">
+        <v>683.11</v>
+      </c>
+      <c r="F98" t="n">
+        <v>683.37</v>
+      </c>
+      <c r="G98" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="H98" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I98" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>715.04</v>
+      </c>
+      <c r="D99" t="n">
+        <v>715.04</v>
+      </c>
+      <c r="E99" t="n">
+        <v>671.63</v>
+      </c>
+      <c r="F99" t="n">
+        <v>671.63</v>
+      </c>
+      <c r="G99" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="H99" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I99" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:07</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>711.75</v>
+      </c>
+      <c r="D100" t="n">
+        <v>711.75</v>
+      </c>
+      <c r="E100" t="n">
+        <v>662.96</v>
+      </c>
+      <c r="F100" t="n">
+        <v>662.96</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="H100" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I100" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4029,7 +4257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7613,6 +7841,234 @@
         <v>83.3</v>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>285.77</v>
+      </c>
+      <c r="D95" t="n">
+        <v>285.77</v>
+      </c>
+      <c r="E95" t="n">
+        <v>267.39</v>
+      </c>
+      <c r="F95" t="n">
+        <v>275.74</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="H95" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I95" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>283.76</v>
+      </c>
+      <c r="D96" t="n">
+        <v>283.76</v>
+      </c>
+      <c r="E96" t="n">
+        <v>267.39</v>
+      </c>
+      <c r="F96" t="n">
+        <v>268.52</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H96" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I96" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="D97" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="E97" t="n">
+        <v>262.08</v>
+      </c>
+      <c r="F97" t="n">
+        <v>263.19</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="H97" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I97" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:08</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>286.02</v>
+      </c>
+      <c r="D98" t="n">
+        <v>286.02</v>
+      </c>
+      <c r="E98" t="n">
+        <v>267.41</v>
+      </c>
+      <c r="F98" t="n">
+        <v>275.65</v>
+      </c>
+      <c r="G98" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H98" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I98" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:08</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>284.01</v>
+      </c>
+      <c r="D99" t="n">
+        <v>284.01</v>
+      </c>
+      <c r="E99" t="n">
+        <v>267.41</v>
+      </c>
+      <c r="F99" t="n">
+        <v>268.44</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H99" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I99" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>282</v>
+      </c>
+      <c r="D100" t="n">
+        <v>282</v>
+      </c>
+      <c r="E100" t="n">
+        <v>262.1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>263.11</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="H100" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I100" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -7629,7 +8085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11213,6 +11669,234 @@
         <v>81.7</v>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>391.12</v>
+      </c>
+      <c r="D95" t="n">
+        <v>471.01</v>
+      </c>
+      <c r="E95" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="F95" t="n">
+        <v>456.86</v>
+      </c>
+      <c r="G95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I95" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>388.44</v>
+      </c>
+      <c r="D96" t="n">
+        <v>458.97</v>
+      </c>
+      <c r="E96" t="n">
+        <v>380.35</v>
+      </c>
+      <c r="F96" t="n">
+        <v>445.19</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="H96" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I96" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:46</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>385.76</v>
+      </c>
+      <c r="D97" t="n">
+        <v>458.97</v>
+      </c>
+      <c r="E97" t="n">
+        <v>372.98</v>
+      </c>
+      <c r="F97" t="n">
+        <v>436.56</v>
+      </c>
+      <c r="G97" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="H97" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I97" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>391.16</v>
+      </c>
+      <c r="D98" t="n">
+        <v>470.36</v>
+      </c>
+      <c r="E98" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="F98" t="n">
+        <v>458.52</v>
+      </c>
+      <c r="G98" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H98" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I98" t="n">
+        <v>85</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>388.47</v>
+      </c>
+      <c r="D99" t="n">
+        <v>458.34</v>
+      </c>
+      <c r="E99" t="n">
+        <v>380.45</v>
+      </c>
+      <c r="F99" t="n">
+        <v>446.81</v>
+      </c>
+      <c r="G99" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="H99" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I99" t="n">
+        <v>85</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>385.79</v>
+      </c>
+      <c r="D100" t="n">
+        <v>458.34</v>
+      </c>
+      <c r="E100" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="F100" t="n">
+        <v>438.15</v>
+      </c>
+      <c r="G100" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="H100" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I100" t="n">
+        <v>85</v>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -11229,7 +11913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14243,234 @@
         <v>81.7</v>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:47</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>237.95</v>
+      </c>
+      <c r="D62" t="n">
+        <v>240.71</v>
+      </c>
+      <c r="E62" t="n">
+        <v>212.54</v>
+      </c>
+      <c r="F62" t="n">
+        <v>240.71</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-3.13</v>
+      </c>
+      <c r="H62" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:47</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>235.4</v>
+      </c>
+      <c r="D63" t="n">
+        <v>235.4</v>
+      </c>
+      <c r="E63" t="n">
+        <v>212.54</v>
+      </c>
+      <c r="F63" t="n">
+        <v>231.22</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="H63" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:47</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>232.85</v>
+      </c>
+      <c r="D64" t="n">
+        <v>232.85</v>
+      </c>
+      <c r="E64" t="n">
+        <v>206.09</v>
+      </c>
+      <c r="F64" t="n">
+        <v>224.2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="H64" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>238.28</v>
+      </c>
+      <c r="D65" t="n">
+        <v>240.83</v>
+      </c>
+      <c r="E65" t="n">
+        <v>212.58</v>
+      </c>
+      <c r="F65" t="n">
+        <v>240.83</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="H65" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I65" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>235.73</v>
+      </c>
+      <c r="D66" t="n">
+        <v>235.73</v>
+      </c>
+      <c r="E66" t="n">
+        <v>212.58</v>
+      </c>
+      <c r="F66" t="n">
+        <v>231.33</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="H66" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I66" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>233.18</v>
+      </c>
+      <c r="D67" t="n">
+        <v>233.18</v>
+      </c>
+      <c r="E67" t="n">
+        <v>206.13</v>
+      </c>
+      <c r="F67" t="n">
+        <v>224.31</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-9.74</v>
+      </c>
+      <c r="H67" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I67" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -13575,7 +14487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14884,6 +15796,234 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:47</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>533.45</v>
+      </c>
+      <c r="D35" t="n">
+        <v>705.04</v>
+      </c>
+      <c r="E35" t="n">
+        <v>533.45</v>
+      </c>
+      <c r="F35" t="n">
+        <v>705.04</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H35" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I35" t="n">
+        <v>85</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:47</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>526.75</v>
+      </c>
+      <c r="D36" t="n">
+        <v>672.59</v>
+      </c>
+      <c r="E36" t="n">
+        <v>526.75</v>
+      </c>
+      <c r="F36" t="n">
+        <v>672.59</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I36" t="n">
+        <v>85</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:34:47</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>520.05</v>
+      </c>
+      <c r="D37" t="n">
+        <v>662.83</v>
+      </c>
+      <c r="E37" t="n">
+        <v>520.05</v>
+      </c>
+      <c r="F37" t="n">
+        <v>648.6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="H37" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I37" t="n">
+        <v>85</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>533.49</v>
+      </c>
+      <c r="D38" t="n">
+        <v>705.41</v>
+      </c>
+      <c r="E38" t="n">
+        <v>533.49</v>
+      </c>
+      <c r="F38" t="n">
+        <v>705.41</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="H38" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I38" t="n">
+        <v>85</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>526.8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>672.9400000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>526.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>672.9400000000001</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I39" t="n">
+        <v>85</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-16 14:51:09</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>520.1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>662.62</v>
+      </c>
+      <c r="E40" t="n">
+        <v>520.1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>648.9400000000001</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="H40" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I40" t="n">
+        <v>85</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4241,6 +4241,120 @@
         <v>83.3</v>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>718.75</v>
+      </c>
+      <c r="D101" t="n">
+        <v>718.75</v>
+      </c>
+      <c r="E101" t="n">
+        <v>683.3200000000001</v>
+      </c>
+      <c r="F101" t="n">
+        <v>684.37</v>
+      </c>
+      <c r="G101" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="H101" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I101" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>715.45</v>
+      </c>
+      <c r="D102" t="n">
+        <v>715.45</v>
+      </c>
+      <c r="E102" t="n">
+        <v>672.62</v>
+      </c>
+      <c r="F102" t="n">
+        <v>672.62</v>
+      </c>
+      <c r="G102" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="H102" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I102" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>712.16</v>
+      </c>
+      <c r="D103" t="n">
+        <v>712.16</v>
+      </c>
+      <c r="E103" t="n">
+        <v>663.9299999999999</v>
+      </c>
+      <c r="F103" t="n">
+        <v>663.9299999999999</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-5.14</v>
+      </c>
+      <c r="H103" t="n">
+        <v>699.9400000000001</v>
+      </c>
+      <c r="I103" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4257,7 +4371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8069,6 +8183,120 @@
         <v>83.3</v>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>285.96</v>
+      </c>
+      <c r="D101" t="n">
+        <v>285.96</v>
+      </c>
+      <c r="E101" t="n">
+        <v>267.59</v>
+      </c>
+      <c r="F101" t="n">
+        <v>275.3</v>
+      </c>
+      <c r="G101" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H101" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I101" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>283.94</v>
+      </c>
+      <c r="D102" t="n">
+        <v>283.94</v>
+      </c>
+      <c r="E102" t="n">
+        <v>267.59</v>
+      </c>
+      <c r="F102" t="n">
+        <v>268.1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H102" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I102" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>281.93</v>
+      </c>
+      <c r="D103" t="n">
+        <v>281.93</v>
+      </c>
+      <c r="E103" t="n">
+        <v>262.28</v>
+      </c>
+      <c r="F103" t="n">
+        <v>262.77</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="H103" t="n">
+        <v>266.43</v>
+      </c>
+      <c r="I103" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -8085,7 +8313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11897,6 +12125,120 @@
         <v>85</v>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>390.29</v>
+      </c>
+      <c r="D101" t="n">
+        <v>582.39</v>
+      </c>
+      <c r="E101" t="n">
+        <v>383.44</v>
+      </c>
+      <c r="F101" t="n">
+        <v>582.39</v>
+      </c>
+      <c r="G101" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="H101" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I101" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>387.61</v>
+      </c>
+      <c r="D102" t="n">
+        <v>457.76</v>
+      </c>
+      <c r="E102" t="n">
+        <v>383.44</v>
+      </c>
+      <c r="F102" t="n">
+        <v>445.54</v>
+      </c>
+      <c r="G102" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="H102" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I102" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:44</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="D103" t="n">
+        <v>457.76</v>
+      </c>
+      <c r="E103" t="n">
+        <v>324.18</v>
+      </c>
+      <c r="F103" t="n">
+        <v>324.18</v>
+      </c>
+      <c r="G103" t="n">
+        <v>-21.17</v>
+      </c>
+      <c r="H103" t="n">
+        <v>411.22</v>
+      </c>
+      <c r="I103" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -11913,7 +12255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14471,6 +14813,120 @@
         <v>83.3</v>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:45</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>238.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>240.81</v>
+      </c>
+      <c r="E68" t="n">
+        <v>212.69</v>
+      </c>
+      <c r="F68" t="n">
+        <v>240.81</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:45</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="D69" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="E69" t="n">
+        <v>212.69</v>
+      </c>
+      <c r="F69" t="n">
+        <v>231.3</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="H69" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I69" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:45</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="E70" t="n">
+        <v>206.23</v>
+      </c>
+      <c r="F70" t="n">
+        <v>224.28</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-9.75</v>
+      </c>
+      <c r="H70" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="I70" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -14487,7 +14943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16024,6 +16480,120 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>533.27</v>
+      </c>
+      <c r="D41" t="n">
+        <v>705.1900000000001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>533.27</v>
+      </c>
+      <c r="F41" t="n">
+        <v>705.1900000000001</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I41" t="n">
+        <v>85</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:45</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>526.58</v>
+      </c>
+      <c r="D42" t="n">
+        <v>672.73</v>
+      </c>
+      <c r="E42" t="n">
+        <v>526.58</v>
+      </c>
+      <c r="F42" t="n">
+        <v>672.73</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H42" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I42" t="n">
+        <v>85</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:12:45</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>519.88</v>
+      </c>
+      <c r="D43" t="n">
+        <v>662.75</v>
+      </c>
+      <c r="E43" t="n">
+        <v>519.88</v>
+      </c>
+      <c r="F43" t="n">
+        <v>648.74</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>671.58</v>
+      </c>
+      <c r="I43" t="n">
+        <v>85</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4355,6 +4355,576 @@
         <v>83.3</v>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:48</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>728.95</v>
+      </c>
+      <c r="D104" t="n">
+        <v>732.39</v>
+      </c>
+      <c r="E104" t="n">
+        <v>696.62</v>
+      </c>
+      <c r="F104" t="n">
+        <v>696.62</v>
+      </c>
+      <c r="G104" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="H104" t="n">
+        <v>700.61</v>
+      </c>
+      <c r="I104" t="n">
+        <v>85</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:48</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>725.95</v>
+      </c>
+      <c r="D105" t="n">
+        <v>725.95</v>
+      </c>
+      <c r="E105" t="n">
+        <v>685.86</v>
+      </c>
+      <c r="F105" t="n">
+        <v>685.86</v>
+      </c>
+      <c r="G105" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="H105" t="n">
+        <v>700.61</v>
+      </c>
+      <c r="I105" t="n">
+        <v>85</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:48</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>722.95</v>
+      </c>
+      <c r="D106" t="n">
+        <v>722.95</v>
+      </c>
+      <c r="E106" t="n">
+        <v>677.91</v>
+      </c>
+      <c r="F106" t="n">
+        <v>677.91</v>
+      </c>
+      <c r="G106" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="H106" t="n">
+        <v>700.61</v>
+      </c>
+      <c r="I106" t="n">
+        <v>85</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>727.53</v>
+      </c>
+      <c r="D107" t="n">
+        <v>734.36</v>
+      </c>
+      <c r="E107" t="n">
+        <v>694.39</v>
+      </c>
+      <c r="F107" t="n">
+        <v>694.39</v>
+      </c>
+      <c r="G107" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="H107" t="n">
+        <v>700.35</v>
+      </c>
+      <c r="I107" t="n">
+        <v>85</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>724.53</v>
+      </c>
+      <c r="D108" t="n">
+        <v>724.53</v>
+      </c>
+      <c r="E108" t="n">
+        <v>683.65</v>
+      </c>
+      <c r="F108" t="n">
+        <v>683.65</v>
+      </c>
+      <c r="G108" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="H108" t="n">
+        <v>700.35</v>
+      </c>
+      <c r="I108" t="n">
+        <v>85</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>721.53</v>
+      </c>
+      <c r="D109" t="n">
+        <v>723</v>
+      </c>
+      <c r="E109" t="n">
+        <v>675.7</v>
+      </c>
+      <c r="F109" t="n">
+        <v>675.7</v>
+      </c>
+      <c r="G109" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="H109" t="n">
+        <v>700.35</v>
+      </c>
+      <c r="I109" t="n">
+        <v>85</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:49</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>727.3099999999999</v>
+      </c>
+      <c r="D110" t="n">
+        <v>734.5</v>
+      </c>
+      <c r="E110" t="n">
+        <v>693.17</v>
+      </c>
+      <c r="F110" t="n">
+        <v>734.5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H110" t="n">
+        <v>700.5599999999999</v>
+      </c>
+      <c r="I110" t="n">
+        <v>85</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:49</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>724.3099999999999</v>
+      </c>
+      <c r="D111" t="n">
+        <v>724.3099999999999</v>
+      </c>
+      <c r="E111" t="n">
+        <v>682.46</v>
+      </c>
+      <c r="F111" t="n">
+        <v>682.46</v>
+      </c>
+      <c r="G111" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="H111" t="n">
+        <v>700.5599999999999</v>
+      </c>
+      <c r="I111" t="n">
+        <v>85</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:49</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>721.3200000000001</v>
+      </c>
+      <c r="D112" t="n">
+        <v>722.84</v>
+      </c>
+      <c r="E112" t="n">
+        <v>656.29</v>
+      </c>
+      <c r="F112" t="n">
+        <v>656.29</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="H112" t="n">
+        <v>700.5599999999999</v>
+      </c>
+      <c r="I112" t="n">
+        <v>85</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:52</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>726.88</v>
+      </c>
+      <c r="D113" t="n">
+        <v>733.97</v>
+      </c>
+      <c r="E113" t="n">
+        <v>692.67</v>
+      </c>
+      <c r="F113" t="n">
+        <v>733.97</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H113" t="n">
+        <v>700.55</v>
+      </c>
+      <c r="I113" t="n">
+        <v>85</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:52</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>723.89</v>
+      </c>
+      <c r="D114" t="n">
+        <v>723.89</v>
+      </c>
+      <c r="E114" t="n">
+        <v>681.97</v>
+      </c>
+      <c r="F114" t="n">
+        <v>681.97</v>
+      </c>
+      <c r="G114" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="H114" t="n">
+        <v>700.55</v>
+      </c>
+      <c r="I114" t="n">
+        <v>85</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:52</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>720.9</v>
+      </c>
+      <c r="D115" t="n">
+        <v>722.61</v>
+      </c>
+      <c r="E115" t="n">
+        <v>655.8099999999999</v>
+      </c>
+      <c r="F115" t="n">
+        <v>655.8099999999999</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="H115" t="n">
+        <v>700.55</v>
+      </c>
+      <c r="I115" t="n">
+        <v>85</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>726.64</v>
+      </c>
+      <c r="D116" t="n">
+        <v>733.75</v>
+      </c>
+      <c r="E116" t="n">
+        <v>692.45</v>
+      </c>
+      <c r="F116" t="n">
+        <v>733.75</v>
+      </c>
+      <c r="G116" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H116" t="n">
+        <v>700.61</v>
+      </c>
+      <c r="I116" t="n">
+        <v>85</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>723.65</v>
+      </c>
+      <c r="D117" t="n">
+        <v>723.65</v>
+      </c>
+      <c r="E117" t="n">
+        <v>681.76</v>
+      </c>
+      <c r="F117" t="n">
+        <v>681.76</v>
+      </c>
+      <c r="G117" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="H117" t="n">
+        <v>700.61</v>
+      </c>
+      <c r="I117" t="n">
+        <v>85</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>720.66</v>
+      </c>
+      <c r="D118" t="n">
+        <v>722.39</v>
+      </c>
+      <c r="E118" t="n">
+        <v>655.61</v>
+      </c>
+      <c r="F118" t="n">
+        <v>655.61</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-6.42</v>
+      </c>
+      <c r="H118" t="n">
+        <v>700.61</v>
+      </c>
+      <c r="I118" t="n">
+        <v>85</v>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4371,7 +4941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8297,6 +8867,576 @@
         <v>83.3</v>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:48</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>283.48</v>
+      </c>
+      <c r="D104" t="n">
+        <v>283.48</v>
+      </c>
+      <c r="E104" t="n">
+        <v>266.57</v>
+      </c>
+      <c r="F104" t="n">
+        <v>276.72</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="H104" t="n">
+        <v>263.96</v>
+      </c>
+      <c r="I104" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:48</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>281.5</v>
+      </c>
+      <c r="D105" t="n">
+        <v>281.5</v>
+      </c>
+      <c r="E105" t="n">
+        <v>266.57</v>
+      </c>
+      <c r="F105" t="n">
+        <v>269.51</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>263.96</v>
+      </c>
+      <c r="I105" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:48</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>279.52</v>
+      </c>
+      <c r="D106" t="n">
+        <v>279.52</v>
+      </c>
+      <c r="E106" t="n">
+        <v>261.3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>264.18</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H106" t="n">
+        <v>263.96</v>
+      </c>
+      <c r="I106" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>283.41</v>
+      </c>
+      <c r="D107" t="n">
+        <v>283.41</v>
+      </c>
+      <c r="E107" t="n">
+        <v>266.51</v>
+      </c>
+      <c r="F107" t="n">
+        <v>276.59</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="H107" t="n">
+        <v>263.69</v>
+      </c>
+      <c r="I107" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>281.42</v>
+      </c>
+      <c r="D108" t="n">
+        <v>281.42</v>
+      </c>
+      <c r="E108" t="n">
+        <v>266.51</v>
+      </c>
+      <c r="F108" t="n">
+        <v>269.37</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H108" t="n">
+        <v>263.69</v>
+      </c>
+      <c r="I108" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>279.43</v>
+      </c>
+      <c r="D109" t="n">
+        <v>279.43</v>
+      </c>
+      <c r="E109" t="n">
+        <v>261.23</v>
+      </c>
+      <c r="F109" t="n">
+        <v>264.03</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H109" t="n">
+        <v>263.69</v>
+      </c>
+      <c r="I109" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:50</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>283.63</v>
+      </c>
+      <c r="D110" t="n">
+        <v>283.63</v>
+      </c>
+      <c r="E110" t="n">
+        <v>266.42</v>
+      </c>
+      <c r="F110" t="n">
+        <v>274.05</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H110" t="n">
+        <v>263.92</v>
+      </c>
+      <c r="I110" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:50</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>281.64</v>
+      </c>
+      <c r="D111" t="n">
+        <v>281.64</v>
+      </c>
+      <c r="E111" t="n">
+        <v>266.42</v>
+      </c>
+      <c r="F111" t="n">
+        <v>269.08</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H111" t="n">
+        <v>263.92</v>
+      </c>
+      <c r="I111" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:50</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>279.66</v>
+      </c>
+      <c r="D112" t="n">
+        <v>279.66</v>
+      </c>
+      <c r="E112" t="n">
+        <v>254.46</v>
+      </c>
+      <c r="F112" t="n">
+        <v>254.46</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-3.58</v>
+      </c>
+      <c r="H112" t="n">
+        <v>263.92</v>
+      </c>
+      <c r="I112" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="D113" t="n">
+        <v>283.7</v>
+      </c>
+      <c r="E113" t="n">
+        <v>266.29</v>
+      </c>
+      <c r="F113" t="n">
+        <v>274.13</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H113" t="n">
+        <v>264.22</v>
+      </c>
+      <c r="I113" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>281.72</v>
+      </c>
+      <c r="D114" t="n">
+        <v>281.72</v>
+      </c>
+      <c r="E114" t="n">
+        <v>266.29</v>
+      </c>
+      <c r="F114" t="n">
+        <v>269.16</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H114" t="n">
+        <v>264.22</v>
+      </c>
+      <c r="I114" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>279.74</v>
+      </c>
+      <c r="D115" t="n">
+        <v>279.74</v>
+      </c>
+      <c r="E115" t="n">
+        <v>254.54</v>
+      </c>
+      <c r="F115" t="n">
+        <v>254.54</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="H115" t="n">
+        <v>264.22</v>
+      </c>
+      <c r="I115" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>283.77</v>
+      </c>
+      <c r="D116" t="n">
+        <v>283.77</v>
+      </c>
+      <c r="E116" t="n">
+        <v>266.24</v>
+      </c>
+      <c r="F116" t="n">
+        <v>274.11</v>
+      </c>
+      <c r="G116" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="H116" t="n">
+        <v>264.18</v>
+      </c>
+      <c r="I116" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>281.79</v>
+      </c>
+      <c r="D117" t="n">
+        <v>281.79</v>
+      </c>
+      <c r="E117" t="n">
+        <v>266.24</v>
+      </c>
+      <c r="F117" t="n">
+        <v>269.14</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H117" t="n">
+        <v>264.18</v>
+      </c>
+      <c r="I117" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>279.81</v>
+      </c>
+      <c r="D118" t="n">
+        <v>279.81</v>
+      </c>
+      <c r="E118" t="n">
+        <v>254.52</v>
+      </c>
+      <c r="F118" t="n">
+        <v>254.52</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="H118" t="n">
+        <v>264.18</v>
+      </c>
+      <c r="I118" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -8313,7 +9453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12239,6 +13379,576 @@
         <v>83.3</v>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="D104" t="n">
+        <v>513.25</v>
+      </c>
+      <c r="E104" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="F104" t="n">
+        <v>483.79</v>
+      </c>
+      <c r="G104" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="H104" t="n">
+        <v>418.68</v>
+      </c>
+      <c r="I104" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="D105" t="n">
+        <v>497.61</v>
+      </c>
+      <c r="E105" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="F105" t="n">
+        <v>469.05</v>
+      </c>
+      <c r="G105" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="H105" t="n">
+        <v>418.68</v>
+      </c>
+      <c r="I105" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>346.68</v>
+      </c>
+      <c r="D106" t="n">
+        <v>497.61</v>
+      </c>
+      <c r="E106" t="n">
+        <v>346.68</v>
+      </c>
+      <c r="F106" t="n">
+        <v>458.16</v>
+      </c>
+      <c r="G106" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="H106" t="n">
+        <v>418.68</v>
+      </c>
+      <c r="I106" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="D107" t="n">
+        <v>511.27</v>
+      </c>
+      <c r="E107" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="F107" t="n">
+        <v>489.45</v>
+      </c>
+      <c r="G107" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>417.62</v>
+      </c>
+      <c r="I107" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>354.17</v>
+      </c>
+      <c r="D108" t="n">
+        <v>495.66</v>
+      </c>
+      <c r="E108" t="n">
+        <v>354.17</v>
+      </c>
+      <c r="F108" t="n">
+        <v>474.5</v>
+      </c>
+      <c r="G108" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="H108" t="n">
+        <v>417.62</v>
+      </c>
+      <c r="I108" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>351.23</v>
+      </c>
+      <c r="D109" t="n">
+        <v>495.66</v>
+      </c>
+      <c r="E109" t="n">
+        <v>351.23</v>
+      </c>
+      <c r="F109" t="n">
+        <v>463.46</v>
+      </c>
+      <c r="G109" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="H109" t="n">
+        <v>417.62</v>
+      </c>
+      <c r="I109" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="D110" t="n">
+        <v>598.37</v>
+      </c>
+      <c r="E110" t="n">
+        <v>358.79</v>
+      </c>
+      <c r="F110" t="n">
+        <v>598.37</v>
+      </c>
+      <c r="G110" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="H110" t="n">
+        <v>419.17</v>
+      </c>
+      <c r="I110" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="D111" t="n">
+        <v>495.85</v>
+      </c>
+      <c r="E111" t="n">
+        <v>355.85</v>
+      </c>
+      <c r="F111" t="n">
+        <v>477.66</v>
+      </c>
+      <c r="G111" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="H111" t="n">
+        <v>419.17</v>
+      </c>
+      <c r="I111" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="D112" t="n">
+        <v>495.85</v>
+      </c>
+      <c r="E112" t="n">
+        <v>352.9</v>
+      </c>
+      <c r="F112" t="n">
+        <v>367.11</v>
+      </c>
+      <c r="G112" t="n">
+        <v>-12.42</v>
+      </c>
+      <c r="H112" t="n">
+        <v>419.17</v>
+      </c>
+      <c r="I112" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>359.42</v>
+      </c>
+      <c r="D113" t="n">
+        <v>599.2</v>
+      </c>
+      <c r="E113" t="n">
+        <v>359.42</v>
+      </c>
+      <c r="F113" t="n">
+        <v>599.2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>42.92</v>
+      </c>
+      <c r="H113" t="n">
+        <v>419.24</v>
+      </c>
+      <c r="I113" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="D114" t="n">
+        <v>495.76</v>
+      </c>
+      <c r="E114" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="F114" t="n">
+        <v>479.24</v>
+      </c>
+      <c r="G114" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="H114" t="n">
+        <v>419.24</v>
+      </c>
+      <c r="I114" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>353.52</v>
+      </c>
+      <c r="D115" t="n">
+        <v>495.76</v>
+      </c>
+      <c r="E115" t="n">
+        <v>353.52</v>
+      </c>
+      <c r="F115" t="n">
+        <v>370.66</v>
+      </c>
+      <c r="G115" t="n">
+        <v>-11.59</v>
+      </c>
+      <c r="H115" t="n">
+        <v>419.24</v>
+      </c>
+      <c r="I115" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>359.82</v>
+      </c>
+      <c r="D116" t="n">
+        <v>599.05</v>
+      </c>
+      <c r="E116" t="n">
+        <v>359.82</v>
+      </c>
+      <c r="F116" t="n">
+        <v>599.05</v>
+      </c>
+      <c r="G116" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="H116" t="n">
+        <v>417.79</v>
+      </c>
+      <c r="I116" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>356.86</v>
+      </c>
+      <c r="D117" t="n">
+        <v>495.75</v>
+      </c>
+      <c r="E117" t="n">
+        <v>356.86</v>
+      </c>
+      <c r="F117" t="n">
+        <v>479.17</v>
+      </c>
+      <c r="G117" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="H117" t="n">
+        <v>417.79</v>
+      </c>
+      <c r="I117" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="D118" t="n">
+        <v>495.75</v>
+      </c>
+      <c r="E118" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="F118" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-11.27</v>
+      </c>
+      <c r="H118" t="n">
+        <v>417.79</v>
+      </c>
+      <c r="I118" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -12255,7 +13965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14927,6 +16637,576 @@
         <v>83.3</v>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>238.63</v>
+      </c>
+      <c r="D71" t="n">
+        <v>243.25</v>
+      </c>
+      <c r="E71" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="F71" t="n">
+        <v>243.25</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="H71" t="n">
+        <v>249.16</v>
+      </c>
+      <c r="I71" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>236.26</v>
+      </c>
+      <c r="D72" t="n">
+        <v>236.26</v>
+      </c>
+      <c r="E72" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="F72" t="n">
+        <v>234.33</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-5.95</v>
+      </c>
+      <c r="H72" t="n">
+        <v>249.16</v>
+      </c>
+      <c r="I72" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>233.89</v>
+      </c>
+      <c r="D73" t="n">
+        <v>233.89</v>
+      </c>
+      <c r="E73" t="n">
+        <v>208.37</v>
+      </c>
+      <c r="F73" t="n">
+        <v>227.74</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="H73" t="n">
+        <v>249.16</v>
+      </c>
+      <c r="I73" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>238.69</v>
+      </c>
+      <c r="D74" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="F74" t="n">
+        <v>243.4</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="H74" t="n">
+        <v>248.87</v>
+      </c>
+      <c r="I74" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>236.32</v>
+      </c>
+      <c r="D75" t="n">
+        <v>236.32</v>
+      </c>
+      <c r="E75" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>234.46</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-5.79</v>
+      </c>
+      <c r="H75" t="n">
+        <v>248.87</v>
+      </c>
+      <c r="I75" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:30</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>233.95</v>
+      </c>
+      <c r="D76" t="n">
+        <v>233.95</v>
+      </c>
+      <c r="E76" t="n">
+        <v>208.26</v>
+      </c>
+      <c r="F76" t="n">
+        <v>227.86</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="H76" t="n">
+        <v>248.87</v>
+      </c>
+      <c r="I76" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>238.59</v>
+      </c>
+      <c r="D77" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="E77" t="n">
+        <v>214.54</v>
+      </c>
+      <c r="F77" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="H77" t="n">
+        <v>249.01</v>
+      </c>
+      <c r="I77" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>236.22</v>
+      </c>
+      <c r="D78" t="n">
+        <v>236.22</v>
+      </c>
+      <c r="E78" t="n">
+        <v>214.54</v>
+      </c>
+      <c r="F78" t="n">
+        <v>234.66</v>
+      </c>
+      <c r="G78" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="H78" t="n">
+        <v>249.01</v>
+      </c>
+      <c r="I78" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>233.85</v>
+      </c>
+      <c r="D79" t="n">
+        <v>233.85</v>
+      </c>
+      <c r="E79" t="n">
+        <v>178.19</v>
+      </c>
+      <c r="F79" t="n">
+        <v>178.19</v>
+      </c>
+      <c r="G79" t="n">
+        <v>-28.44</v>
+      </c>
+      <c r="H79" t="n">
+        <v>249.01</v>
+      </c>
+      <c r="I79" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>238.61</v>
+      </c>
+      <c r="D80" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="E80" t="n">
+        <v>214.72</v>
+      </c>
+      <c r="F80" t="n">
+        <v>306.25</v>
+      </c>
+      <c r="G80" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="H80" t="n">
+        <v>248.67</v>
+      </c>
+      <c r="I80" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>236.23</v>
+      </c>
+      <c r="D81" t="n">
+        <v>236.23</v>
+      </c>
+      <c r="E81" t="n">
+        <v>214.72</v>
+      </c>
+      <c r="F81" t="n">
+        <v>234.7</v>
+      </c>
+      <c r="G81" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="H81" t="n">
+        <v>248.67</v>
+      </c>
+      <c r="I81" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:53</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>233.86</v>
+      </c>
+      <c r="D82" t="n">
+        <v>233.86</v>
+      </c>
+      <c r="E82" t="n">
+        <v>178.22</v>
+      </c>
+      <c r="F82" t="n">
+        <v>178.22</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-28.33</v>
+      </c>
+      <c r="H82" t="n">
+        <v>248.67</v>
+      </c>
+      <c r="I82" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>238.61</v>
+      </c>
+      <c r="D83" t="n">
+        <v>306.31</v>
+      </c>
+      <c r="E83" t="n">
+        <v>214.81</v>
+      </c>
+      <c r="F83" t="n">
+        <v>306.31</v>
+      </c>
+      <c r="G83" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="H83" t="n">
+        <v>248.26</v>
+      </c>
+      <c r="I83" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>236.22</v>
+      </c>
+      <c r="D84" t="n">
+        <v>236.22</v>
+      </c>
+      <c r="E84" t="n">
+        <v>214.81</v>
+      </c>
+      <c r="F84" t="n">
+        <v>234.74</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="H84" t="n">
+        <v>248.26</v>
+      </c>
+      <c r="I84" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:04</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>233.84</v>
+      </c>
+      <c r="D85" t="n">
+        <v>233.84</v>
+      </c>
+      <c r="E85" t="n">
+        <v>178.26</v>
+      </c>
+      <c r="F85" t="n">
+        <v>178.26</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="H85" t="n">
+        <v>248.26</v>
+      </c>
+      <c r="I85" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -14943,7 +17223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16594,6 +18874,576 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>533.17</v>
+      </c>
+      <c r="D44" t="n">
+        <v>673.1799999999999</v>
+      </c>
+      <c r="E44" t="n">
+        <v>533.17</v>
+      </c>
+      <c r="F44" t="n">
+        <v>673.1799999999999</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="H44" t="n">
+        <v>674.36</v>
+      </c>
+      <c r="I44" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>527.14</v>
+      </c>
+      <c r="D45" t="n">
+        <v>668.89</v>
+      </c>
+      <c r="E45" t="n">
+        <v>527.14</v>
+      </c>
+      <c r="F45" t="n">
+        <v>645.17</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="H45" t="n">
+        <v>674.36</v>
+      </c>
+      <c r="I45" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:07:49</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>521.11</v>
+      </c>
+      <c r="D46" t="n">
+        <v>647.4299999999999</v>
+      </c>
+      <c r="E46" t="n">
+        <v>521.11</v>
+      </c>
+      <c r="F46" t="n">
+        <v>624.47</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>674.36</v>
+      </c>
+      <c r="I46" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:31</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>535.22</v>
+      </c>
+      <c r="D47" t="n">
+        <v>673.77</v>
+      </c>
+      <c r="E47" t="n">
+        <v>535.22</v>
+      </c>
+      <c r="F47" t="n">
+        <v>673.77</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H47" t="n">
+        <v>673.38</v>
+      </c>
+      <c r="I47" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:31</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>529.15</v>
+      </c>
+      <c r="D48" t="n">
+        <v>670.16</v>
+      </c>
+      <c r="E48" t="n">
+        <v>529.15</v>
+      </c>
+      <c r="F48" t="n">
+        <v>645.6799999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="H48" t="n">
+        <v>673.38</v>
+      </c>
+      <c r="I48" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:20:31</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>523.09</v>
+      </c>
+      <c r="D49" t="n">
+        <v>648.62</v>
+      </c>
+      <c r="E49" t="n">
+        <v>523.09</v>
+      </c>
+      <c r="F49" t="n">
+        <v>624.92</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="H49" t="n">
+        <v>673.38</v>
+      </c>
+      <c r="I49" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>537.97</v>
+      </c>
+      <c r="D50" t="n">
+        <v>676.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>537.97</v>
+      </c>
+      <c r="F50" t="n">
+        <v>673.92</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="H50" t="n">
+        <v>674.1799999999999</v>
+      </c>
+      <c r="I50" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>531.88</v>
+      </c>
+      <c r="D51" t="n">
+        <v>672.83</v>
+      </c>
+      <c r="E51" t="n">
+        <v>531.88</v>
+      </c>
+      <c r="F51" t="n">
+        <v>645.87</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>674.1799999999999</v>
+      </c>
+      <c r="I51" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:37:51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>525.8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>651.24</v>
+      </c>
+      <c r="E52" t="n">
+        <v>525.8</v>
+      </c>
+      <c r="F52" t="n">
+        <v>625.14</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-7.27</v>
+      </c>
+      <c r="H52" t="n">
+        <v>674.1799999999999</v>
+      </c>
+      <c r="I52" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:54</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>538.67</v>
+      </c>
+      <c r="D53" t="n">
+        <v>676.85</v>
+      </c>
+      <c r="E53" t="n">
+        <v>538.67</v>
+      </c>
+      <c r="F53" t="n">
+        <v>673.5599999999999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H53" t="n">
+        <v>673.9299999999999</v>
+      </c>
+      <c r="I53" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:54</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>532.58</v>
+      </c>
+      <c r="D54" t="n">
+        <v>673.21</v>
+      </c>
+      <c r="E54" t="n">
+        <v>532.58</v>
+      </c>
+      <c r="F54" t="n">
+        <v>645.52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="H54" t="n">
+        <v>673.9299999999999</v>
+      </c>
+      <c r="I54" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-04-17 02:57:54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>526.48</v>
+      </c>
+      <c r="D55" t="n">
+        <v>651.59</v>
+      </c>
+      <c r="E55" t="n">
+        <v>526.48</v>
+      </c>
+      <c r="F55" t="n">
+        <v>624.79</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="H55" t="n">
+        <v>673.9299999999999</v>
+      </c>
+      <c r="I55" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:05</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>538.8</v>
+      </c>
+      <c r="D56" t="n">
+        <v>676.8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>538.8</v>
+      </c>
+      <c r="F56" t="n">
+        <v>673.49</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H56" t="n">
+        <v>673.39</v>
+      </c>
+      <c r="I56" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>532.7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>673.23</v>
+      </c>
+      <c r="E57" t="n">
+        <v>532.7</v>
+      </c>
+      <c r="F57" t="n">
+        <v>645.42</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="H57" t="n">
+        <v>673.39</v>
+      </c>
+      <c r="I57" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-04-17 03:14:05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>526.59</v>
+      </c>
+      <c r="D58" t="n">
+        <v>651.59</v>
+      </c>
+      <c r="E58" t="n">
+        <v>526.59</v>
+      </c>
+      <c r="F58" t="n">
+        <v>624.67</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-7.24</v>
+      </c>
+      <c r="H58" t="n">
+        <v>673.39</v>
+      </c>
+      <c r="I58" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4925,6 +4925,234 @@
         <v>85</v>
       </c>
       <c r="J118" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>740.23</v>
+      </c>
+      <c r="D119" t="n">
+        <v>740.23</v>
+      </c>
+      <c r="E119" t="n">
+        <v>677.95</v>
+      </c>
+      <c r="F119" t="n">
+        <v>677.95</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="H119" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="I119" t="n">
+        <v>85</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>737.6900000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>737.6900000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>669.21</v>
+      </c>
+      <c r="F120" t="n">
+        <v>669.21</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="H120" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="I120" t="n">
+        <v>85</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>735.15</v>
+      </c>
+      <c r="D121" t="n">
+        <v>735.15</v>
+      </c>
+      <c r="E121" t="n">
+        <v>662.74</v>
+      </c>
+      <c r="F121" t="n">
+        <v>662.74</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="H121" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="I121" t="n">
+        <v>85</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:43</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>740.6799999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>740.6799999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>679.6900000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>679.6900000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="H122" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="I122" t="n">
+        <v>85</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:43</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>738.14</v>
+      </c>
+      <c r="D123" t="n">
+        <v>738.14</v>
+      </c>
+      <c r="E123" t="n">
+        <v>670.92</v>
+      </c>
+      <c r="F123" t="n">
+        <v>670.92</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-5.52</v>
+      </c>
+      <c r="H123" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="I123" t="n">
+        <v>85</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:43</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>735.6</v>
+      </c>
+      <c r="D124" t="n">
+        <v>735.6</v>
+      </c>
+      <c r="E124" t="n">
+        <v>664.4400000000001</v>
+      </c>
+      <c r="F124" t="n">
+        <v>664.4400000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-6.43</v>
+      </c>
+      <c r="H124" t="n">
+        <v>710.14</v>
+      </c>
+      <c r="I124" t="n">
+        <v>85</v>
+      </c>
+      <c r="J124" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -4941,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9439,6 +9667,234 @@
       <c r="J118" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>285.29</v>
+      </c>
+      <c r="D119" t="n">
+        <v>285.29</v>
+      </c>
+      <c r="E119" t="n">
+        <v>267.29</v>
+      </c>
+      <c r="F119" t="n">
+        <v>272.72</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H119" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="I119" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>283.2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>283.2</v>
+      </c>
+      <c r="E120" t="n">
+        <v>265.27</v>
+      </c>
+      <c r="F120" t="n">
+        <v>265.27</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="H120" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="I120" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>281.11</v>
+      </c>
+      <c r="D121" t="n">
+        <v>281.11</v>
+      </c>
+      <c r="E121" t="n">
+        <v>259.77</v>
+      </c>
+      <c r="F121" t="n">
+        <v>259.77</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="H121" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="I121" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:43</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>285.17</v>
+      </c>
+      <c r="D122" t="n">
+        <v>285.17</v>
+      </c>
+      <c r="E122" t="n">
+        <v>267.47</v>
+      </c>
+      <c r="F122" t="n">
+        <v>273.08</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H122" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="I122" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:43</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>283.07</v>
+      </c>
+      <c r="D123" t="n">
+        <v>283.07</v>
+      </c>
+      <c r="E123" t="n">
+        <v>265.62</v>
+      </c>
+      <c r="F123" t="n">
+        <v>265.62</v>
+      </c>
+      <c r="G123" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H123" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="I123" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:43</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>280.98</v>
+      </c>
+      <c r="D124" t="n">
+        <v>280.98</v>
+      </c>
+      <c r="E124" t="n">
+        <v>260.11</v>
+      </c>
+      <c r="F124" t="n">
+        <v>260.11</v>
+      </c>
+      <c r="G124" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="H124" t="n">
+        <v>270.23</v>
+      </c>
+      <c r="I124" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -9453,7 +9909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13949,6 +14405,234 @@
         <v>83.3</v>
       </c>
       <c r="J118" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>386.17</v>
+      </c>
+      <c r="D119" t="n">
+        <v>501.2</v>
+      </c>
+      <c r="E119" t="n">
+        <v>386.17</v>
+      </c>
+      <c r="F119" t="n">
+        <v>501.2</v>
+      </c>
+      <c r="G119" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="H119" t="n">
+        <v>422.79</v>
+      </c>
+      <c r="I119" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>382.59</v>
+      </c>
+      <c r="D120" t="n">
+        <v>483.99</v>
+      </c>
+      <c r="E120" t="n">
+        <v>382.59</v>
+      </c>
+      <c r="F120" t="n">
+        <v>483.99</v>
+      </c>
+      <c r="G120" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="H120" t="n">
+        <v>422.79</v>
+      </c>
+      <c r="I120" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:28</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>379.01</v>
+      </c>
+      <c r="D121" t="n">
+        <v>478.16</v>
+      </c>
+      <c r="E121" t="n">
+        <v>379.01</v>
+      </c>
+      <c r="F121" t="n">
+        <v>471.28</v>
+      </c>
+      <c r="G121" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="H121" t="n">
+        <v>422.79</v>
+      </c>
+      <c r="I121" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>389.56</v>
+      </c>
+      <c r="D122" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="E122" t="n">
+        <v>389.56</v>
+      </c>
+      <c r="F122" t="n">
+        <v>502.4</v>
+      </c>
+      <c r="G122" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="H122" t="n">
+        <v>422.79</v>
+      </c>
+      <c r="I122" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="D123" t="n">
+        <v>485.15</v>
+      </c>
+      <c r="E123" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="F123" t="n">
+        <v>485.15</v>
+      </c>
+      <c r="G123" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="H123" t="n">
+        <v>422.79</v>
+      </c>
+      <c r="I123" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="D124" t="n">
+        <v>478.17</v>
+      </c>
+      <c r="E124" t="n">
+        <v>382.33</v>
+      </c>
+      <c r="F124" t="n">
+        <v>472.41</v>
+      </c>
+      <c r="G124" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="H124" t="n">
+        <v>422.79</v>
+      </c>
+      <c r="I124" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J124" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -13965,7 +14649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17207,6 +17891,234 @@
         <v>83.3</v>
       </c>
       <c r="J85" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:29</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>252.94</v>
+      </c>
+      <c r="D86" t="n">
+        <v>252.94</v>
+      </c>
+      <c r="E86" t="n">
+        <v>221.88</v>
+      </c>
+      <c r="F86" t="n">
+        <v>242.15</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="H86" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="I86" t="n">
+        <v>85</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:29</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>250.54</v>
+      </c>
+      <c r="D87" t="n">
+        <v>250.54</v>
+      </c>
+      <c r="E87" t="n">
+        <v>221.88</v>
+      </c>
+      <c r="F87" t="n">
+        <v>233.66</v>
+      </c>
+      <c r="G87" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="H87" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="I87" t="n">
+        <v>85</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>248.14</v>
+      </c>
+      <c r="D88" t="n">
+        <v>248.14</v>
+      </c>
+      <c r="E88" t="n">
+        <v>215.92</v>
+      </c>
+      <c r="F88" t="n">
+        <v>227.37</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="H88" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="I88" t="n">
+        <v>85</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>253.46</v>
+      </c>
+      <c r="D89" t="n">
+        <v>253.46</v>
+      </c>
+      <c r="E89" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="F89" t="n">
+        <v>241.88</v>
+      </c>
+      <c r="G89" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="H89" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="I89" t="n">
+        <v>85</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>251.06</v>
+      </c>
+      <c r="D90" t="n">
+        <v>251.06</v>
+      </c>
+      <c r="E90" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="F90" t="n">
+        <v>233.39</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-6.85</v>
+      </c>
+      <c r="H90" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="I90" t="n">
+        <v>85</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>248.65</v>
+      </c>
+      <c r="D91" t="n">
+        <v>248.65</v>
+      </c>
+      <c r="E91" t="n">
+        <v>216.42</v>
+      </c>
+      <c r="F91" t="n">
+        <v>227.11</v>
+      </c>
+      <c r="G91" t="n">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="H91" t="n">
+        <v>250.56</v>
+      </c>
+      <c r="I91" t="n">
+        <v>85</v>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -17223,7 +18135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19444,6 +20356,234 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:29</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>651.12</v>
+      </c>
+      <c r="D59" t="n">
+        <v>779.0599999999999</v>
+      </c>
+      <c r="E59" t="n">
+        <v>651.12</v>
+      </c>
+      <c r="F59" t="n">
+        <v>779.0599999999999</v>
+      </c>
+      <c r="G59" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="H59" t="n">
+        <v>688.55</v>
+      </c>
+      <c r="I59" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:29</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>644.61</v>
+      </c>
+      <c r="D60" t="n">
+        <v>707.13</v>
+      </c>
+      <c r="E60" t="n">
+        <v>644.61</v>
+      </c>
+      <c r="F60" t="n">
+        <v>707.13</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H60" t="n">
+        <v>688.55</v>
+      </c>
+      <c r="I60" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:40:29</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>638.1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>599.86</v>
+      </c>
+      <c r="F61" t="n">
+        <v>599.86</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-12.88</v>
+      </c>
+      <c r="H61" t="n">
+        <v>688.55</v>
+      </c>
+      <c r="I61" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>651.09</v>
+      </c>
+      <c r="D62" t="n">
+        <v>735.65</v>
+      </c>
+      <c r="E62" t="n">
+        <v>651.09</v>
+      </c>
+      <c r="F62" t="n">
+        <v>735.65</v>
+      </c>
+      <c r="G62" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="H62" t="n">
+        <v>688.55</v>
+      </c>
+      <c r="I62" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>644.58</v>
+      </c>
+      <c r="D63" t="n">
+        <v>708.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>644.58</v>
+      </c>
+      <c r="F63" t="n">
+        <v>708.5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H63" t="n">
+        <v>688.55</v>
+      </c>
+      <c r="I63" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-04-18 18:12:44</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>638.0700000000001</v>
+      </c>
+      <c r="D64" t="n">
+        <v>688.4299999999999</v>
+      </c>
+      <c r="E64" t="n">
+        <v>638.0700000000001</v>
+      </c>
+      <c r="F64" t="n">
+        <v>688.4299999999999</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H64" t="n">
+        <v>688.55</v>
+      </c>
+      <c r="I64" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stock_predictions.xlsx
+++ b/stock_predictions.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5153,6 +5153,120 @@
         <v>85</v>
       </c>
       <c r="J124" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>706.52</v>
+      </c>
+      <c r="D125" t="n">
+        <v>716.0700000000001</v>
+      </c>
+      <c r="E125" t="n">
+        <v>689.59</v>
+      </c>
+      <c r="F125" t="n">
+        <v>692.03</v>
+      </c>
+      <c r="G125" t="n">
+        <v>-3.07</v>
+      </c>
+      <c r="H125" t="n">
+        <v>713.9400000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>703.88</v>
+      </c>
+      <c r="D126" t="n">
+        <v>706.02</v>
+      </c>
+      <c r="E126" t="n">
+        <v>682.33</v>
+      </c>
+      <c r="F126" t="n">
+        <v>682.33</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-4.43</v>
+      </c>
+      <c r="H126" t="n">
+        <v>713.9400000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>701.24</v>
+      </c>
+      <c r="D127" t="n">
+        <v>706.02</v>
+      </c>
+      <c r="E127" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="F127" t="n">
+        <v>675.15</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="H127" t="n">
+        <v>713.9400000000001</v>
+      </c>
+      <c r="I127" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -5169,7 +5283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9895,6 +10009,120 @@
       <c r="J124" t="inlineStr">
         <is>
           <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>283.01</v>
+      </c>
+      <c r="D125" t="n">
+        <v>283.01</v>
+      </c>
+      <c r="E125" t="n">
+        <v>277.23</v>
+      </c>
+      <c r="F125" t="n">
+        <v>281.53</v>
+      </c>
+      <c r="G125" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="H125" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="I125" t="n">
+        <v>80</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>280.08</v>
+      </c>
+      <c r="D126" t="n">
+        <v>280.08</v>
+      </c>
+      <c r="E126" t="n">
+        <v>270.77</v>
+      </c>
+      <c r="F126" t="n">
+        <v>270.77</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="H126" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="I126" t="n">
+        <v>80</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="D127" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="E127" t="n">
+        <v>262.82</v>
+      </c>
+      <c r="F127" t="n">
+        <v>262.82</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="H127" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="I127" t="n">
+        <v>80</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -9909,7 +10137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14633,6 +14861,120 @@
         <v>83.3</v>
       </c>
       <c r="J124" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>454.83</v>
+      </c>
+      <c r="D125" t="n">
+        <v>502.12</v>
+      </c>
+      <c r="E125" t="n">
+        <v>440.44</v>
+      </c>
+      <c r="F125" t="n">
+        <v>502.12</v>
+      </c>
+      <c r="G125" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="H125" t="n">
+        <v>424.62</v>
+      </c>
+      <c r="I125" t="n">
+        <v>80</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>450.04</v>
+      </c>
+      <c r="D126" t="n">
+        <v>482.59</v>
+      </c>
+      <c r="E126" t="n">
+        <v>440.44</v>
+      </c>
+      <c r="F126" t="n">
+        <v>482.59</v>
+      </c>
+      <c r="G126" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="H126" t="n">
+        <v>424.62</v>
+      </c>
+      <c r="I126" t="n">
+        <v>80</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>445.24</v>
+      </c>
+      <c r="D127" t="n">
+        <v>468.15</v>
+      </c>
+      <c r="E127" t="n">
+        <v>427.26</v>
+      </c>
+      <c r="F127" t="n">
+        <v>468.15</v>
+      </c>
+      <c r="G127" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="H127" t="n">
+        <v>424.62</v>
+      </c>
+      <c r="I127" t="n">
+        <v>80</v>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t>STRONG BUY</t>
         </is>
@@ -14649,7 +14991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18119,6 +18461,120 @@
         <v>85</v>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="D92" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="E92" t="n">
+        <v>224.43</v>
+      </c>
+      <c r="F92" t="n">
+        <v>232.44</v>
+      </c>
+      <c r="G92" t="n">
+        <v>-11.95</v>
+      </c>
+      <c r="H92" t="n">
+        <v>263.99</v>
+      </c>
+      <c r="I92" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>246.33</v>
+      </c>
+      <c r="D93" t="n">
+        <v>246.33</v>
+      </c>
+      <c r="E93" t="n">
+        <v>224.43</v>
+      </c>
+      <c r="F93" t="n">
+        <v>226.87</v>
+      </c>
+      <c r="G93" t="n">
+        <v>-14.06</v>
+      </c>
+      <c r="H93" t="n">
+        <v>263.99</v>
+      </c>
+      <c r="I93" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:14</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>244.73</v>
+      </c>
+      <c r="D94" t="n">
+        <v>244.73</v>
+      </c>
+      <c r="E94" t="n">
+        <v>220.35</v>
+      </c>
+      <c r="F94" t="n">
+        <v>222.75</v>
+      </c>
+      <c r="G94" t="n">
+        <v>-15.62</v>
+      </c>
+      <c r="H94" t="n">
+        <v>263.99</v>
+      </c>
+      <c r="I94" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="J94" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
@@ -18135,7 +18591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20584,6 +21040,120 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:15</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Best Case</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>759.4400000000001</v>
+      </c>
+      <c r="D65" t="n">
+        <v>794.75</v>
+      </c>
+      <c r="E65" t="n">
+        <v>751.55</v>
+      </c>
+      <c r="F65" t="n">
+        <v>764.09</v>
+      </c>
+      <c r="G65" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="H65" t="n">
+        <v>675.03</v>
+      </c>
+      <c r="I65" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:15</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Average Case</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>752</v>
+      </c>
+      <c r="D66" t="n">
+        <v>766.01</v>
+      </c>
+      <c r="E66" t="n">
+        <v>736.46</v>
+      </c>
+      <c r="F66" t="n">
+        <v>736.46</v>
+      </c>
+      <c r="G66" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>675.03</v>
+      </c>
+      <c r="I66" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-25 19:13:15</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>744.5700000000001</v>
+      </c>
+      <c r="D67" t="n">
+        <v>766.01</v>
+      </c>
+      <c r="E67" t="n">
+        <v>716.03</v>
+      </c>
+      <c r="F67" t="n">
+        <v>716.03</v>
+      </c>
+      <c r="G67" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="H67" t="n">
+        <v>675.03</v>
+      </c>
+      <c r="I67" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
